--- a/Resources/Crosswalks and Schemas.xlsx
+++ b/Resources/Crosswalks and Schemas.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHDTJB\Documents\LocalSave\Code\R\GitHub\WA-DOH-CHS-Death-Files-ETL\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE066D68-F62F-4D92-9310-E17FCF6AE668}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2BCE403B-DF8E-4A3F-A5E0-A5CA6AF1DDD2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8280" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-20520" yWindow="-16365" windowWidth="29040" windowHeight="15720" firstSheet="1" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="3" r:id="rId1"/>
@@ -21,14 +21,16 @@
     <sheet name="schema_factors" sheetId="6" r:id="rId6"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">harmonized_data_schema!$A$1:$H$285</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">recode_variables!$A$1:$I$432</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">schema_factors!$A$1:$G$219</definedName>
   </definedNames>
   <calcPr calcId="124519"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6101" uniqueCount="622">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6107" uniqueCount="622">
   <si>
     <t>to_name</t>
   </si>
@@ -1985,7 +1987,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2061,6 +2063,22 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -17591,7 +17609,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51D60DD1-DC0B-4658-A996-7DC0B41964ED}">
-  <dimension ref="A1:H283"/>
+  <dimension ref="A1:H285"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="14.42578125" style="16" customWidth="1"/>
@@ -17978,53 +17996,57 @@
         <v>0</v>
       </c>
       <c r="E19" s="23">
-        <v>3</v>
-      </c>
-      <c r="F19" s="21" t="s">
-        <v>426</v>
+        <v>1</v>
+      </c>
+      <c r="F19" s="23" t="s">
+        <v>419</v>
       </c>
       <c r="G19" s="24"/>
       <c r="H19" s="22"/>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A20" s="16">
+    <row r="20" spans="1:8" s="34" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A20" s="29">
         <v>9</v>
       </c>
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="C20" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D20" s="28" t="b">
+      <c r="C20" s="29" t="s">
+        <v>525</v>
+      </c>
+      <c r="D20" s="30" t="b">
         <v>0</v>
       </c>
       <c r="E20" s="7">
-        <v>4</v>
-      </c>
-      <c r="F20" s="16" t="s">
-        <v>428</v>
-      </c>
-    </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A21" s="16">
+        <v>2</v>
+      </c>
+      <c r="F20" s="7" t="s">
+        <v>422</v>
+      </c>
+      <c r="G20" s="32"/>
+      <c r="H20" s="33"/>
+    </row>
+    <row r="21" spans="1:8" s="34" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A21" s="29">
         <v>9</v>
       </c>
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="C21" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D21" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E21" s="7">
-        <v>5</v>
-      </c>
-      <c r="F21" s="16" t="s">
-        <v>431</v>
-      </c>
+      <c r="C21" s="29" t="s">
+        <v>525</v>
+      </c>
+      <c r="D21" s="30" t="b">
+        <v>0</v>
+      </c>
+      <c r="E21" s="31">
+        <v>3</v>
+      </c>
+      <c r="F21" s="29" t="s">
+        <v>426</v>
+      </c>
+      <c r="G21" s="32"/>
+      <c r="H21" s="33"/>
     </row>
     <row r="22" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A22" s="16">
@@ -18040,10 +18062,10 @@
         <v>0</v>
       </c>
       <c r="E22" s="7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F22" s="16" t="s">
-        <v>435</v>
+        <v>428</v>
       </c>
     </row>
     <row r="23" spans="1:8" x14ac:dyDescent="0.25">
@@ -18060,10 +18082,10 @@
         <v>0</v>
       </c>
       <c r="E23" s="7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F23" s="16" t="s">
-        <v>439</v>
+        <v>431</v>
       </c>
     </row>
     <row r="24" spans="1:8" x14ac:dyDescent="0.25">
@@ -18080,10 +18102,10 @@
         <v>0</v>
       </c>
       <c r="E24" s="7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F24" s="16" t="s">
-        <v>455</v>
+        <v>435</v>
       </c>
     </row>
     <row r="25" spans="1:8" x14ac:dyDescent="0.25">
@@ -18100,50 +18122,58 @@
         <v>0</v>
       </c>
       <c r="E25" s="7">
+        <v>7</v>
+      </c>
+      <c r="F25" s="16" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A26" s="16">
         <v>9</v>
       </c>
-      <c r="F25" s="16" t="s">
+      <c r="B26" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D26" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E26" s="7">
+        <v>8</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>455</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A27" s="16">
+        <v>9</v>
+      </c>
+      <c r="B27" s="7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D27" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E27" s="7">
+        <v>9</v>
+      </c>
+      <c r="F27" s="16" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="26" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="22">
+    <row r="28" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A28" s="22">
         <v>10</v>
       </c>
-      <c r="B26" s="21" t="s">
+      <c r="B28" s="21" t="s">
         <v>529</v>
-      </c>
-      <c r="C26" s="21" t="s">
-        <v>530</v>
-      </c>
-      <c r="D26" s="27"/>
-      <c r="E26" s="21"/>
-      <c r="F26" s="21"/>
-      <c r="G26" s="24"/>
-      <c r="H26" s="22"/>
-    </row>
-    <row r="27" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="21">
-        <v>11</v>
-      </c>
-      <c r="B27" s="21" t="s">
-        <v>18</v>
-      </c>
-      <c r="C27" s="21" t="s">
-        <v>530</v>
-      </c>
-      <c r="D27" s="27"/>
-      <c r="E27" s="21"/>
-      <c r="F27" s="21"/>
-      <c r="G27" s="24"/>
-      <c r="H27" s="22"/>
-    </row>
-    <row r="28" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="21">
-        <v>12</v>
-      </c>
-      <c r="B28" s="21" t="s">
-        <v>20</v>
       </c>
       <c r="C28" s="21" t="s">
         <v>530</v>
@@ -18156,65 +18186,57 @@
     </row>
     <row r="29" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A29" s="21">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B29" s="21" t="s">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="C29" s="21" t="s">
-        <v>525</v>
-      </c>
-      <c r="D29" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="E29" s="23" t="s">
-        <v>460</v>
-      </c>
-      <c r="F29" s="21" t="s">
-        <v>539</v>
-      </c>
+        <v>530</v>
+      </c>
+      <c r="D29" s="27"/>
+      <c r="E29" s="21"/>
+      <c r="F29" s="21"/>
       <c r="G29" s="24"/>
       <c r="H29" s="22"/>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A30" s="16">
+    <row r="30" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A30" s="21">
+        <v>12</v>
+      </c>
+      <c r="B30" s="21" t="s">
+        <v>20</v>
+      </c>
+      <c r="C30" s="21" t="s">
+        <v>530</v>
+      </c>
+      <c r="D30" s="27"/>
+      <c r="E30" s="21"/>
+      <c r="F30" s="21"/>
+      <c r="G30" s="24"/>
+      <c r="H30" s="22"/>
+    </row>
+    <row r="31" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="21">
         <v>13</v>
       </c>
-      <c r="B30" s="16" t="s">
+      <c r="B31" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="C30" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D30" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E30" s="7" t="s">
-        <v>514</v>
-      </c>
-      <c r="F30" s="16" t="s">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A31" s="16">
-        <v>13</v>
-      </c>
-      <c r="B31" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="C31" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D31" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E31" s="7" t="s">
-        <v>445</v>
-      </c>
-      <c r="F31" s="16" t="s">
-        <v>541</v>
-      </c>
+      <c r="C31" s="21" t="s">
+        <v>525</v>
+      </c>
+      <c r="D31" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="E31" s="23" t="s">
+        <v>460</v>
+      </c>
+      <c r="F31" s="21" t="s">
+        <v>539</v>
+      </c>
+      <c r="G31" s="24"/>
+      <c r="H31" s="22"/>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A32" s="16">
@@ -18230,10 +18252,10 @@
         <v>0</v>
       </c>
       <c r="E32" s="7" t="s">
-        <v>453</v>
+        <v>514</v>
       </c>
       <c r="F32" s="16" t="s">
-        <v>542</v>
+        <v>540</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -18250,10 +18272,10 @@
         <v>0</v>
       </c>
       <c r="E33" s="7" t="s">
-        <v>521</v>
+        <v>445</v>
       </c>
       <c r="F33" s="16" t="s">
-        <v>543</v>
+        <v>541</v>
       </c>
     </row>
     <row r="34" spans="1:8" x14ac:dyDescent="0.25">
@@ -18270,10 +18292,10 @@
         <v>0</v>
       </c>
       <c r="E34" s="7" t="s">
-        <v>467</v>
+        <v>453</v>
       </c>
       <c r="F34" s="16" t="s">
-        <v>544</v>
+        <v>542</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -18290,53 +18312,61 @@
         <v>0</v>
       </c>
       <c r="E35" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="F35" s="16" t="s">
+        <v>543</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A36" s="16">
+        <v>13</v>
+      </c>
+      <c r="B36" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C36" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D36" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E36" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="F36" s="16" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A37" s="16">
+        <v>13</v>
+      </c>
+      <c r="B37" s="16" t="s">
+        <v>22</v>
+      </c>
+      <c r="C37" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D37" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E37" s="7" t="s">
         <v>414</v>
       </c>
-      <c r="F35" s="16" t="s">
+      <c r="F37" s="16" t="s">
         <v>406</v>
       </c>
-    </row>
-    <row r="36" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="21">
-        <v>14</v>
-      </c>
-      <c r="B36" s="21" t="s">
-        <v>24</v>
-      </c>
-      <c r="C36" s="21" t="s">
-        <v>530</v>
-      </c>
-      <c r="D36" s="27"/>
-      <c r="E36" s="21"/>
-      <c r="F36" s="21"/>
-      <c r="G36" s="24"/>
-      <c r="H36" s="22"/>
-    </row>
-    <row r="37" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="21">
-        <v>15</v>
-      </c>
-      <c r="B37" s="21" t="s">
-        <v>26</v>
-      </c>
-      <c r="C37" s="21" t="s">
-        <v>530</v>
-      </c>
-      <c r="D37" s="27"/>
-      <c r="E37" s="21"/>
-      <c r="F37" s="21"/>
-      <c r="G37" s="24"/>
-      <c r="H37" s="22"/>
     </row>
     <row r="38" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A38" s="21">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B38" s="21" t="s">
-        <v>27</v>
-      </c>
-      <c r="C38" s="23" t="s">
-        <v>527</v>
+        <v>24</v>
+      </c>
+      <c r="C38" s="21" t="s">
+        <v>530</v>
       </c>
       <c r="D38" s="27"/>
       <c r="E38" s="21"/>
@@ -18346,13 +18376,13 @@
     </row>
     <row r="39" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A39" s="21">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B39" s="21" t="s">
-        <v>28</v>
-      </c>
-      <c r="C39" s="23" t="s">
-        <v>527</v>
+        <v>26</v>
+      </c>
+      <c r="C39" s="21" t="s">
+        <v>530</v>
       </c>
       <c r="D39" s="27"/>
       <c r="E39" s="21"/>
@@ -18362,10 +18392,10 @@
     </row>
     <row r="40" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A40" s="21">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B40" s="21" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C40" s="23" t="s">
         <v>527</v>
@@ -18378,10 +18408,10 @@
     </row>
     <row r="41" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A41" s="21">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="B41" s="21" t="s">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="C41" s="23" t="s">
         <v>527</v>
@@ -18394,10 +18424,10 @@
     </row>
     <row r="42" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A42" s="21">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B42" s="21" t="s">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="C42" s="23" t="s">
         <v>527</v>
@@ -18410,10 +18440,10 @@
     </row>
     <row r="43" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A43" s="21">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="B43" s="21" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C43" s="23" t="s">
         <v>527</v>
@@ -18426,10 +18456,10 @@
     </row>
     <row r="44" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A44" s="21">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B44" s="21" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C44" s="23" t="s">
         <v>527</v>
@@ -18442,65 +18472,57 @@
     </row>
     <row r="45" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A45" s="21">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="B45" s="21" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C45" s="23" t="s">
-        <v>525</v>
-      </c>
-      <c r="D45" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="E45" s="23" t="s">
-        <v>443</v>
-      </c>
-      <c r="F45" s="21" t="s">
-        <v>442</v>
-      </c>
+        <v>527</v>
+      </c>
+      <c r="D45" s="27"/>
+      <c r="E45" s="21"/>
+      <c r="F45" s="21"/>
       <c r="G45" s="24"/>
       <c r="H45" s="22"/>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A46" s="16">
+    <row r="46" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="21">
+        <v>22</v>
+      </c>
+      <c r="B46" s="21" t="s">
+        <v>38</v>
+      </c>
+      <c r="C46" s="23" t="s">
+        <v>527</v>
+      </c>
+      <c r="D46" s="27"/>
+      <c r="E46" s="21"/>
+      <c r="F46" s="21"/>
+      <c r="G46" s="24"/>
+      <c r="H46" s="22"/>
+    </row>
+    <row r="47" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A47" s="21">
         <v>23</v>
       </c>
-      <c r="B46" s="16" t="s">
+      <c r="B47" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="C46" s="7" t="s">
-        <v>525</v>
-      </c>
-      <c r="D46" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E46" s="7" t="s">
-        <v>445</v>
-      </c>
-      <c r="F46" s="16" t="s">
-        <v>444</v>
-      </c>
-    </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A47" s="16">
-        <v>23</v>
-      </c>
-      <c r="B47" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="C47" s="7" t="s">
-        <v>525</v>
-      </c>
-      <c r="D47" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E47" s="7" t="s">
-        <v>447</v>
-      </c>
-      <c r="F47" s="16" t="s">
-        <v>446</v>
-      </c>
+      <c r="C47" s="23" t="s">
+        <v>525</v>
+      </c>
+      <c r="D47" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="E47" s="23" t="s">
+        <v>443</v>
+      </c>
+      <c r="F47" s="21" t="s">
+        <v>442</v>
+      </c>
+      <c r="G47" s="24"/>
+      <c r="H47" s="22"/>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="16">
@@ -18516,10 +18538,10 @@
         <v>0</v>
       </c>
       <c r="E48" s="7" t="s">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="F48" s="16" t="s">
-        <v>450</v>
+        <v>444</v>
       </c>
     </row>
     <row r="49" spans="1:8" x14ac:dyDescent="0.25">
@@ -18536,10 +18558,10 @@
         <v>0</v>
       </c>
       <c r="E49" s="7" t="s">
-        <v>412</v>
+        <v>447</v>
       </c>
       <c r="F49" s="16" t="s">
-        <v>451</v>
+        <v>446</v>
       </c>
     </row>
     <row r="50" spans="1:8" x14ac:dyDescent="0.25">
@@ -18556,10 +18578,10 @@
         <v>0</v>
       </c>
       <c r="E50" s="7" t="s">
-        <v>453</v>
+        <v>449</v>
       </c>
       <c r="F50" s="16" t="s">
-        <v>452</v>
+        <v>450</v>
       </c>
     </row>
     <row r="51" spans="1:8" x14ac:dyDescent="0.25">
@@ -18576,10 +18598,10 @@
         <v>0</v>
       </c>
       <c r="E51" s="7" t="s">
-        <v>454</v>
+        <v>412</v>
       </c>
       <c r="F51" s="16" t="s">
-        <v>441</v>
+        <v>451</v>
       </c>
     </row>
     <row r="52" spans="1:8" x14ac:dyDescent="0.25">
@@ -18596,97 +18618,91 @@
         <v>0</v>
       </c>
       <c r="E52" s="7" t="s">
+        <v>453</v>
+      </c>
+      <c r="F52" s="16" t="s">
+        <v>452</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A53" s="16">
+        <v>23</v>
+      </c>
+      <c r="B53" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C53" s="7" t="s">
+        <v>525</v>
+      </c>
+      <c r="D53" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E53" s="7" t="s">
+        <v>454</v>
+      </c>
+      <c r="F53" s="16" t="s">
+        <v>441</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A54" s="16">
+        <v>23</v>
+      </c>
+      <c r="B54" s="16" t="s">
+        <v>40</v>
+      </c>
+      <c r="C54" s="7" t="s">
+        <v>525</v>
+      </c>
+      <c r="D54" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E54" s="7" t="s">
         <v>414</v>
       </c>
-      <c r="F52" s="16" t="s">
+      <c r="F54" s="16" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="53" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="21">
+    <row r="55" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A55" s="21">
         <v>24</v>
       </c>
-      <c r="B53" s="21" t="s">
+      <c r="B55" s="21" t="s">
         <v>42</v>
       </c>
-      <c r="C53" s="21" t="s">
+      <c r="C55" s="21" t="s">
         <v>530</v>
       </c>
-      <c r="D53" s="27"/>
-      <c r="E53" s="21"/>
-      <c r="F53" s="21"/>
-      <c r="G53" s="24"/>
-      <c r="H53" s="22"/>
-    </row>
-    <row r="54" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="21">
+      <c r="D55" s="27"/>
+      <c r="E55" s="21"/>
+      <c r="F55" s="21"/>
+      <c r="G55" s="24"/>
+      <c r="H55" s="22"/>
+    </row>
+    <row r="56" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A56" s="21">
         <v>25</v>
       </c>
-      <c r="B54" s="21" t="s">
+      <c r="B56" s="21" t="s">
         <v>44</v>
       </c>
-      <c r="C54" s="21" t="s">
-        <v>525</v>
-      </c>
-      <c r="D54" s="27" t="b">
+      <c r="C56" s="21" t="s">
+        <v>525</v>
+      </c>
+      <c r="D56" s="27" t="b">
         <v>1</v>
       </c>
-      <c r="E54" s="23">
+      <c r="E56" s="23">
         <v>1</v>
       </c>
-      <c r="F54" s="21" t="s">
+      <c r="F56" s="21" t="s">
         <v>485</v>
       </c>
-      <c r="G54" s="26">
+      <c r="G56" s="26">
         <v>1</v>
       </c>
-      <c r="H54" s="22"/>
-    </row>
-    <row r="55" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A55" s="16">
-        <v>25</v>
-      </c>
-      <c r="B55" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="C55" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D55" s="28" t="b">
-        <v>1</v>
-      </c>
-      <c r="E55" s="7">
-        <v>2</v>
-      </c>
-      <c r="F55" s="16" t="s">
-        <v>489</v>
-      </c>
-      <c r="G55" s="20">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="56" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A56" s="16">
-        <v>25</v>
-      </c>
-      <c r="B56" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="C56" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D56" s="28" t="b">
-        <v>1</v>
-      </c>
-      <c r="E56" s="7">
-        <v>3</v>
-      </c>
-      <c r="F56" s="16" t="s">
-        <v>492</v>
-      </c>
-      <c r="G56" s="20">
-        <v>3</v>
-      </c>
+      <c r="H56" s="22"/>
     </row>
     <row r="57" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A57" s="16">
@@ -18702,13 +18718,13 @@
         <v>1</v>
       </c>
       <c r="E57" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F57" s="16" t="s">
-        <v>495</v>
+        <v>489</v>
       </c>
       <c r="G57" s="20">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="58" spans="1:8" x14ac:dyDescent="0.25">
@@ -18725,13 +18741,13 @@
         <v>1</v>
       </c>
       <c r="E58" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F58" s="16" t="s">
-        <v>497</v>
+        <v>492</v>
       </c>
       <c r="G58" s="20">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.25">
@@ -18748,13 +18764,13 @@
         <v>1</v>
       </c>
       <c r="E59" s="7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F59" s="16" t="s">
-        <v>500</v>
+        <v>495</v>
       </c>
       <c r="G59" s="20">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="60" spans="1:8" x14ac:dyDescent="0.25">
@@ -18771,13 +18787,13 @@
         <v>1</v>
       </c>
       <c r="E60" s="7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F60" s="16" t="s">
-        <v>503</v>
+        <v>497</v>
       </c>
       <c r="G60" s="20">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="61" spans="1:8" x14ac:dyDescent="0.25">
@@ -18794,13 +18810,13 @@
         <v>1</v>
       </c>
       <c r="E61" s="7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F61" s="16" t="s">
-        <v>505</v>
+        <v>500</v>
       </c>
       <c r="G61" s="20">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.25">
@@ -18817,45 +18833,44 @@
         <v>1</v>
       </c>
       <c r="E62" s="7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F62" s="16" t="s">
-        <v>406</v>
+        <v>503</v>
       </c>
       <c r="G62" s="20">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="63" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="21">
-        <v>26</v>
-      </c>
-      <c r="B63" s="21" t="s">
-        <v>46</v>
-      </c>
-      <c r="C63" s="21" t="s">
-        <v>525</v>
-      </c>
-      <c r="D63" s="27" t="b">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A63" s="16">
+        <v>25</v>
+      </c>
+      <c r="B63" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="C63" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D63" s="28" t="b">
         <v>1</v>
       </c>
-      <c r="E63" s="23">
-        <v>0</v>
-      </c>
-      <c r="F63" s="21" t="s">
-        <v>545</v>
-      </c>
-      <c r="G63" s="26">
-        <v>1</v>
-      </c>
-      <c r="H63" s="22"/>
+      <c r="E63" s="7">
+        <v>8</v>
+      </c>
+      <c r="F63" s="16" t="s">
+        <v>505</v>
+      </c>
+      <c r="G63" s="20">
+        <v>8</v>
+      </c>
     </row>
     <row r="64" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A64" s="16">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B64" s="16" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C64" s="16" t="s">
         <v>525</v>
@@ -18864,37 +18879,38 @@
         <v>1</v>
       </c>
       <c r="E64" s="7">
+        <v>9</v>
+      </c>
+      <c r="F64" s="16" t="s">
+        <v>406</v>
+      </c>
+      <c r="G64" s="20">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A65" s="21">
+        <v>26</v>
+      </c>
+      <c r="B65" s="21" t="s">
+        <v>46</v>
+      </c>
+      <c r="C65" s="21" t="s">
+        <v>525</v>
+      </c>
+      <c r="D65" s="27" t="b">
         <v>1</v>
       </c>
-      <c r="F64" s="16" t="s">
-        <v>546</v>
-      </c>
-      <c r="G64" s="20">
-        <v>2</v>
-      </c>
-    </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A65" s="16">
-        <v>26</v>
-      </c>
-      <c r="B65" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="C65" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D65" s="28" t="b">
+      <c r="E65" s="23">
+        <v>0</v>
+      </c>
+      <c r="F65" s="21" t="s">
+        <v>545</v>
+      </c>
+      <c r="G65" s="26">
         <v>1</v>
       </c>
-      <c r="E65" s="7">
-        <v>2</v>
-      </c>
-      <c r="F65" s="16" t="s">
-        <v>547</v>
-      </c>
-      <c r="G65" s="20">
-        <v>3</v>
-      </c>
+      <c r="H65" s="22"/>
     </row>
     <row r="66" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A66" s="16">
@@ -18910,13 +18926,13 @@
         <v>1</v>
       </c>
       <c r="E66" s="7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F66" s="16" t="s">
-        <v>548</v>
+        <v>546</v>
       </c>
       <c r="G66" s="20">
-        <v>4</v>
+        <v>2</v>
       </c>
     </row>
     <row r="67" spans="1:8" x14ac:dyDescent="0.25">
@@ -18933,13 +18949,13 @@
         <v>1</v>
       </c>
       <c r="E67" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F67" s="16" t="s">
-        <v>549</v>
+        <v>547</v>
       </c>
       <c r="G67" s="20">
-        <v>5</v>
+        <v>3</v>
       </c>
     </row>
     <row r="68" spans="1:8" x14ac:dyDescent="0.25">
@@ -18956,13 +18972,13 @@
         <v>1</v>
       </c>
       <c r="E68" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F68" s="16" t="s">
-        <v>550</v>
+        <v>548</v>
       </c>
       <c r="G68" s="20">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
     <row r="69" spans="1:8" x14ac:dyDescent="0.25">
@@ -18979,13 +18995,13 @@
         <v>1</v>
       </c>
       <c r="E69" s="7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F69" s="16" t="s">
-        <v>551</v>
+        <v>549</v>
       </c>
       <c r="G69" s="20">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
     <row r="70" spans="1:8" x14ac:dyDescent="0.25">
@@ -19002,13 +19018,13 @@
         <v>1</v>
       </c>
       <c r="E70" s="7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F70" s="16" t="s">
-        <v>552</v>
+        <v>550</v>
       </c>
       <c r="G70" s="20">
-        <v>8</v>
+        <v>6</v>
       </c>
     </row>
     <row r="71" spans="1:8" x14ac:dyDescent="0.25">
@@ -19025,13 +19041,13 @@
         <v>1</v>
       </c>
       <c r="E71" s="7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F71" s="16" t="s">
-        <v>553</v>
+        <v>551</v>
       </c>
       <c r="G71" s="20">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="72" spans="1:8" x14ac:dyDescent="0.25">
@@ -19048,216 +19064,222 @@
         <v>1</v>
       </c>
       <c r="E72" s="7">
+        <v>7</v>
+      </c>
+      <c r="F72" s="16" t="s">
+        <v>552</v>
+      </c>
+      <c r="G72" s="20">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A73" s="16">
+        <v>26</v>
+      </c>
+      <c r="B73" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="C73" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D73" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="E73" s="7">
+        <v>8</v>
+      </c>
+      <c r="F73" s="16" t="s">
+        <v>553</v>
+      </c>
+      <c r="G73" s="20">
         <v>9</v>
       </c>
-      <c r="F72" s="16" t="s">
+    </row>
+    <row r="74" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A74" s="16">
+        <v>26</v>
+      </c>
+      <c r="B74" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="C74" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D74" s="28" t="b">
+        <v>1</v>
+      </c>
+      <c r="E74" s="7">
+        <v>9</v>
+      </c>
+      <c r="F74" s="16" t="s">
         <v>406</v>
       </c>
-      <c r="G72" s="20">
+      <c r="G74" s="20">
         <v>10</v>
       </c>
     </row>
-    <row r="73" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="21">
+    <row r="75" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A75" s="21">
         <v>27</v>
       </c>
-      <c r="B73" s="23" t="s">
+      <c r="B75" s="23" t="s">
         <v>393</v>
       </c>
-      <c r="C73" s="21" t="s">
+      <c r="C75" s="21" t="s">
         <v>524</v>
       </c>
-      <c r="D73" s="27"/>
-      <c r="E73" s="21"/>
-      <c r="F73" s="21"/>
-      <c r="G73" s="24"/>
-      <c r="H73" s="22"/>
-    </row>
-    <row r="74" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="21">
+      <c r="D75" s="27"/>
+      <c r="E75" s="21"/>
+      <c r="F75" s="21"/>
+      <c r="G75" s="24"/>
+      <c r="H75" s="22"/>
+    </row>
+    <row r="76" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A76" s="21">
         <v>28</v>
       </c>
-      <c r="B74" s="21" t="s">
+      <c r="B76" s="21" t="s">
         <v>48</v>
       </c>
-      <c r="C74" s="21" t="s">
-        <v>525</v>
-      </c>
-      <c r="D74" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="E74" s="21" t="s">
+      <c r="C76" s="21" t="s">
+        <v>525</v>
+      </c>
+      <c r="D76" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="E76" s="21" t="s">
         <v>409</v>
       </c>
-      <c r="F74" s="21" t="s">
+      <c r="F76" s="21" t="s">
         <v>408</v>
       </c>
-      <c r="G74" s="24"/>
-      <c r="H74" s="22"/>
-    </row>
-    <row r="75" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A75" s="16">
+      <c r="G76" s="24"/>
+      <c r="H76" s="22"/>
+    </row>
+    <row r="77" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A77" s="16">
         <v>28</v>
       </c>
-      <c r="B75" s="16" t="s">
+      <c r="B77" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C75" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D75" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E75" s="16" t="s">
+      <c r="C77" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D77" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E77" s="16" t="s">
         <v>412</v>
       </c>
-      <c r="F75" s="16" t="s">
+      <c r="F77" s="16" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="76" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A76" s="16">
-        <v>28</v>
-      </c>
-      <c r="B76" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="C76" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D76" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E76" s="16" t="s">
-        <v>414</v>
-      </c>
-      <c r="F76" s="16" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="77" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="21">
-        <v>29</v>
-      </c>
-      <c r="B77" s="21" t="s">
-        <v>50</v>
-      </c>
-      <c r="C77" s="21" t="s">
-        <v>525</v>
-      </c>
-      <c r="D77" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="E77" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="F77" s="21" t="s">
-        <v>408</v>
-      </c>
-      <c r="G77" s="24"/>
-      <c r="H77" s="22"/>
     </row>
     <row r="78" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A78" s="16">
+        <v>28</v>
+      </c>
+      <c r="B78" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="C78" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D78" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E78" s="16" t="s">
+        <v>414</v>
+      </c>
+      <c r="F78" s="16" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A79" s="21">
         <v>29</v>
       </c>
-      <c r="B78" s="16" t="s">
+      <c r="B79" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="C78" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D78" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E78" s="16" t="s">
+      <c r="C79" s="21" t="s">
+        <v>525</v>
+      </c>
+      <c r="D79" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="E79" s="21" t="s">
+        <v>409</v>
+      </c>
+      <c r="F79" s="21" t="s">
+        <v>408</v>
+      </c>
+      <c r="G79" s="24"/>
+      <c r="H79" s="22"/>
+    </row>
+    <row r="80" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A80" s="16">
+        <v>29</v>
+      </c>
+      <c r="B80" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="C80" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D80" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E80" s="16" t="s">
         <v>412</v>
       </c>
-      <c r="F78" s="16" t="s">
+      <c r="F80" s="16" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="79" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A79" s="16">
-        <v>29</v>
-      </c>
-      <c r="B79" s="16" t="s">
-        <v>50</v>
-      </c>
-      <c r="C79" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D79" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E79" s="16" t="s">
-        <v>414</v>
-      </c>
-      <c r="F79" s="16" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="80" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="21">
-        <v>30</v>
-      </c>
-      <c r="B80" s="21" t="s">
-        <v>52</v>
-      </c>
-      <c r="C80" s="21" t="s">
-        <v>525</v>
-      </c>
-      <c r="D80" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="E80" s="23">
-        <v>0</v>
-      </c>
-      <c r="F80" s="21" t="s">
-        <v>554</v>
-      </c>
-      <c r="G80" s="24"/>
-      <c r="H80" s="22"/>
     </row>
     <row r="81" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A81" s="16">
+        <v>29</v>
+      </c>
+      <c r="B81" s="16" t="s">
+        <v>50</v>
+      </c>
+      <c r="C81" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D81" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E81" s="16" t="s">
+        <v>414</v>
+      </c>
+      <c r="F81" s="16" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A82" s="21">
         <v>30</v>
       </c>
-      <c r="B81" s="16" t="s">
+      <c r="B82" s="21" t="s">
         <v>52</v>
       </c>
-      <c r="C81" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D81" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E81" s="7">
-        <v>1</v>
-      </c>
-      <c r="F81" s="16" t="s">
-        <v>555</v>
-      </c>
-    </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A82" s="16">
-        <v>30</v>
-      </c>
-      <c r="B82" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="C82" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D82" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E82" s="7">
-        <v>2</v>
-      </c>
-      <c r="F82" s="16" t="s">
-        <v>556</v>
-      </c>
+      <c r="C82" s="21" t="s">
+        <v>525</v>
+      </c>
+      <c r="D82" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="E82" s="23">
+        <v>0</v>
+      </c>
+      <c r="F82" s="21" t="s">
+        <v>554</v>
+      </c>
+      <c r="G82" s="24"/>
+      <c r="H82" s="22"/>
     </row>
     <row r="83" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A83" s="16">
@@ -19273,10 +19295,10 @@
         <v>0</v>
       </c>
       <c r="E83" s="7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F83" s="16" t="s">
-        <v>557</v>
+        <v>555</v>
       </c>
     </row>
     <row r="84" spans="1:8" x14ac:dyDescent="0.25">
@@ -19293,10 +19315,10 @@
         <v>0</v>
       </c>
       <c r="E84" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F84" s="16" t="s">
-        <v>558</v>
+        <v>556</v>
       </c>
     </row>
     <row r="85" spans="1:8" x14ac:dyDescent="0.25">
@@ -19313,10 +19335,10 @@
         <v>0</v>
       </c>
       <c r="E85" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F85" s="16" t="s">
-        <v>559</v>
+        <v>557</v>
       </c>
     </row>
     <row r="86" spans="1:8" x14ac:dyDescent="0.25">
@@ -19333,269 +19355,269 @@
         <v>0</v>
       </c>
       <c r="E86" s="7">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F86" s="16" t="s">
-        <v>413</v>
-      </c>
-    </row>
-    <row r="87" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="21">
-        <v>31</v>
-      </c>
-      <c r="B87" s="21" t="s">
-        <v>54</v>
-      </c>
-      <c r="C87" s="21" t="s">
-        <v>525</v>
-      </c>
-      <c r="D87" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="E87" s="23" t="s">
-        <v>409</v>
-      </c>
-      <c r="F87" s="21" t="s">
-        <v>408</v>
-      </c>
-      <c r="G87" s="24"/>
-      <c r="H87" s="22"/>
+        <v>558</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A87" s="16">
+        <v>30</v>
+      </c>
+      <c r="B87" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="C87" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D87" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E87" s="7">
+        <v>5</v>
+      </c>
+      <c r="F87" s="16" t="s">
+        <v>559</v>
+      </c>
     </row>
     <row r="88" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A88" s="16">
+        <v>30</v>
+      </c>
+      <c r="B88" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="C88" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D88" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E88" s="7">
+        <v>9</v>
+      </c>
+      <c r="F88" s="16" t="s">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A89" s="21">
         <v>31</v>
       </c>
-      <c r="B88" s="16" t="s">
+      <c r="B89" s="21" t="s">
         <v>54</v>
       </c>
-      <c r="C88" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D88" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E88" s="7" t="s">
+      <c r="C89" s="21" t="s">
+        <v>525</v>
+      </c>
+      <c r="D89" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="E89" s="23" t="s">
+        <v>409</v>
+      </c>
+      <c r="F89" s="21" t="s">
+        <v>408</v>
+      </c>
+      <c r="G89" s="24"/>
+      <c r="H89" s="22"/>
+    </row>
+    <row r="90" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A90" s="16">
+        <v>31</v>
+      </c>
+      <c r="B90" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="C90" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D90" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E90" s="7" t="s">
         <v>412</v>
       </c>
-      <c r="F88" s="16" t="s">
+      <c r="F90" s="16" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="89" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A89" s="16">
-        <v>31</v>
-      </c>
-      <c r="B89" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="C89" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D89" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E89" s="7" t="s">
-        <v>414</v>
-      </c>
-      <c r="F89" s="16" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="90" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="21">
-        <v>32</v>
-      </c>
-      <c r="B90" s="21" t="s">
-        <v>56</v>
-      </c>
-      <c r="C90" s="21" t="s">
-        <v>525</v>
-      </c>
-      <c r="D90" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="E90" s="23" t="s">
-        <v>409</v>
-      </c>
-      <c r="F90" s="21" t="s">
-        <v>408</v>
-      </c>
-      <c r="G90" s="24"/>
-      <c r="H90" s="22"/>
     </row>
     <row r="91" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A91" s="16">
+        <v>31</v>
+      </c>
+      <c r="B91" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="C91" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D91" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E91" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="F91" s="16" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A92" s="21">
         <v>32</v>
       </c>
-      <c r="B91" s="16" t="s">
+      <c r="B92" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="C91" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D91" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E91" s="7" t="s">
+      <c r="C92" s="21" t="s">
+        <v>525</v>
+      </c>
+      <c r="D92" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="E92" s="23" t="s">
+        <v>409</v>
+      </c>
+      <c r="F92" s="21" t="s">
+        <v>408</v>
+      </c>
+      <c r="G92" s="24"/>
+      <c r="H92" s="22"/>
+    </row>
+    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A93" s="16">
+        <v>32</v>
+      </c>
+      <c r="B93" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C93" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D93" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E93" s="7" t="s">
         <v>412</v>
       </c>
-      <c r="F91" s="16" t="s">
+      <c r="F93" s="16" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A92" s="16">
-        <v>32</v>
-      </c>
-      <c r="B92" s="16" t="s">
-        <v>56</v>
-      </c>
-      <c r="C92" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D92" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E92" s="7" t="s">
-        <v>414</v>
-      </c>
-      <c r="F92" s="16" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="93" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="21">
-        <v>33</v>
-      </c>
-      <c r="B93" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="C93" s="21" t="s">
-        <v>525</v>
-      </c>
-      <c r="D93" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="E93" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="F93" s="21" t="s">
-        <v>408</v>
-      </c>
-      <c r="G93" s="24"/>
-      <c r="H93" s="22"/>
     </row>
     <row r="94" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A94" s="16">
+        <v>32</v>
+      </c>
+      <c r="B94" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C94" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D94" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E94" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="F94" s="16" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A95" s="21">
         <v>33</v>
       </c>
-      <c r="B94" s="16" t="s">
+      <c r="B95" s="21" t="s">
         <v>58</v>
       </c>
-      <c r="C94" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D94" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E94" s="16" t="s">
+      <c r="C95" s="21" t="s">
+        <v>525</v>
+      </c>
+      <c r="D95" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="E95" s="21" t="s">
+        <v>409</v>
+      </c>
+      <c r="F95" s="21" t="s">
+        <v>408</v>
+      </c>
+      <c r="G95" s="24"/>
+      <c r="H95" s="22"/>
+    </row>
+    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A96" s="16">
+        <v>33</v>
+      </c>
+      <c r="B96" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C96" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D96" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E96" s="16" t="s">
         <v>412</v>
       </c>
-      <c r="F94" s="16" t="s">
+      <c r="F96" s="16" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="95" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A95" s="16">
+    <row r="97" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A97" s="16">
         <v>33</v>
       </c>
-      <c r="B95" s="16" t="s">
+      <c r="B97" s="16" t="s">
         <v>58</v>
       </c>
-      <c r="C95" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D95" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E95" s="16" t="s">
+      <c r="C97" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D97" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E97" s="16" t="s">
         <v>414</v>
       </c>
-      <c r="F95" s="16" t="s">
+      <c r="F97" s="16" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="96" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="21">
+    <row r="98" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A98" s="21">
         <v>34</v>
       </c>
-      <c r="B96" s="21" t="s">
+      <c r="B98" s="21" t="s">
         <v>60</v>
       </c>
-      <c r="C96" s="21" t="s">
+      <c r="C98" s="21" t="s">
         <v>527</v>
       </c>
-      <c r="D96" s="27"/>
-      <c r="E96" s="21"/>
-      <c r="F96" s="21"/>
-      <c r="G96" s="24"/>
-      <c r="H96" s="22"/>
-    </row>
-    <row r="97" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="21">
+      <c r="D98" s="27"/>
+      <c r="E98" s="21"/>
+      <c r="F98" s="21"/>
+      <c r="G98" s="24"/>
+      <c r="H98" s="22"/>
+    </row>
+    <row r="99" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A99" s="21">
         <v>35</v>
       </c>
-      <c r="B97" s="21" t="s">
+      <c r="B99" s="21" t="s">
         <v>62</v>
       </c>
-      <c r="C97" s="21" t="s">
+      <c r="C99" s="21" t="s">
         <v>527</v>
       </c>
-      <c r="D97" s="27"/>
-      <c r="E97" s="21"/>
-      <c r="F97" s="21"/>
-      <c r="G97" s="24"/>
-      <c r="H97" s="22"/>
-    </row>
-    <row r="98" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A98" s="16">
-        <v>36</v>
-      </c>
-      <c r="B98" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="C98" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D98" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E98" s="7">
-        <v>0</v>
-      </c>
-      <c r="F98" s="16" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="99" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A99" s="16">
-        <v>36</v>
-      </c>
-      <c r="B99" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="C99" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D99" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E99" s="7">
-        <v>1</v>
-      </c>
-      <c r="F99" s="16" t="s">
-        <v>561</v>
-      </c>
+      <c r="D99" s="27"/>
+      <c r="E99" s="21"/>
+      <c r="F99" s="21"/>
+      <c r="G99" s="24"/>
+      <c r="H99" s="22"/>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A100" s="16">
@@ -19611,10 +19633,10 @@
         <v>0</v>
       </c>
       <c r="E100" s="7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F100" s="16" t="s">
-        <v>562</v>
+        <v>560</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.25">
@@ -19631,10 +19653,10 @@
         <v>0</v>
       </c>
       <c r="E101" s="7">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F101" s="16" t="s">
-        <v>563</v>
+        <v>561</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.25">
@@ -19651,10 +19673,10 @@
         <v>0</v>
       </c>
       <c r="E102" s="7">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F102" s="16" t="s">
-        <v>564</v>
+        <v>562</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.25">
@@ -19671,10 +19693,10 @@
         <v>0</v>
       </c>
       <c r="E103" s="7">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F103" s="16" t="s">
-        <v>565</v>
+        <v>563</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.25">
@@ -19691,10 +19713,10 @@
         <v>0</v>
       </c>
       <c r="E104" s="7">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F104" s="16" t="s">
-        <v>566</v>
+        <v>564</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.25">
@@ -19711,10 +19733,10 @@
         <v>0</v>
       </c>
       <c r="E105" s="7">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F105" s="16" t="s">
-        <v>567</v>
+        <v>565</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.25">
@@ -19731,10 +19753,10 @@
         <v>0</v>
       </c>
       <c r="E106" s="7">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F106" s="16" t="s">
-        <v>568</v>
+        <v>566</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.25">
@@ -19751,123 +19773,131 @@
         <v>0</v>
       </c>
       <c r="E107" s="7">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F107" s="16" t="s">
-        <v>516</v>
-      </c>
-    </row>
-    <row r="108" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="21">
-        <v>37</v>
-      </c>
-      <c r="B108" s="21" t="s">
-        <v>66</v>
-      </c>
-      <c r="C108" s="21" t="s">
-        <v>525</v>
-      </c>
-      <c r="D108" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="E108" s="23" t="s">
-        <v>409</v>
-      </c>
-      <c r="F108" s="21" t="s">
-        <v>408</v>
-      </c>
-      <c r="G108" s="24"/>
-      <c r="H108" s="22"/>
+        <v>567</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A108" s="16">
+        <v>36</v>
+      </c>
+      <c r="B108" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="C108" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D108" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E108" s="7">
+        <v>8</v>
+      </c>
+      <c r="F108" s="16" t="s">
+        <v>568</v>
+      </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A109" s="16">
+        <v>36</v>
+      </c>
+      <c r="B109" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="C109" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D109" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E109" s="7">
+        <v>9</v>
+      </c>
+      <c r="F109" s="16" t="s">
+        <v>516</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A110" s="21">
         <v>37</v>
       </c>
-      <c r="B109" s="16" t="s">
+      <c r="B110" s="21" t="s">
         <v>66</v>
       </c>
-      <c r="C109" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D109" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E109" s="7" t="s">
-        <v>412</v>
-      </c>
-      <c r="F109" s="16" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="110" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A110" s="16">
-        <v>37</v>
-      </c>
-      <c r="B110" s="16" t="s">
-        <v>66</v>
-      </c>
-      <c r="C110" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D110" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E110" s="7" t="s">
-        <v>414</v>
-      </c>
-      <c r="F110" s="16" t="s">
-        <v>406</v>
-      </c>
+      <c r="C110" s="21" t="s">
+        <v>525</v>
+      </c>
+      <c r="D110" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="E110" s="23" t="s">
+        <v>409</v>
+      </c>
+      <c r="F110" s="21" t="s">
+        <v>408</v>
+      </c>
+      <c r="G110" s="24"/>
+      <c r="H110" s="22"/>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A111" s="16">
+        <v>37</v>
+      </c>
+      <c r="B111" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="C111" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D111" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E111" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="F111" s="16" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A112" s="16">
+        <v>37</v>
+      </c>
+      <c r="B112" s="16" t="s">
+        <v>66</v>
+      </c>
+      <c r="C112" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D112" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E112" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="F112" s="16" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A113" s="16">
         <v>38</v>
       </c>
-      <c r="B111" s="16" t="s">
+      <c r="B113" s="16" t="s">
         <v>67</v>
       </c>
-      <c r="C111" s="16" t="s">
+      <c r="C113" s="16" t="s">
         <v>527</v>
       </c>
-    </row>
-    <row r="112" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="21">
-        <v>39</v>
-      </c>
-      <c r="B112" s="21" t="s">
-        <v>68</v>
-      </c>
-      <c r="C112" s="21" t="s">
-        <v>527</v>
-      </c>
-      <c r="D112" s="27"/>
-      <c r="E112" s="21"/>
-      <c r="F112" s="21"/>
-      <c r="G112" s="24"/>
-      <c r="H112" s="22"/>
-    </row>
-    <row r="113" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="21">
-        <v>40</v>
-      </c>
-      <c r="B113" s="21" t="s">
-        <v>69</v>
-      </c>
-      <c r="C113" s="21" t="s">
-        <v>527</v>
-      </c>
-      <c r="D113" s="27"/>
-      <c r="E113" s="21"/>
-      <c r="F113" s="21"/>
-      <c r="G113" s="24"/>
-      <c r="H113" s="22"/>
     </row>
     <row r="114" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A114" s="21">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="B114" s="21" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C114" s="21" t="s">
         <v>527</v>
@@ -19880,10 +19910,10 @@
     </row>
     <row r="115" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A115" s="21">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B115" s="21" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C115" s="21" t="s">
         <v>527</v>
@@ -19896,10 +19926,10 @@
     </row>
     <row r="116" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A116" s="21">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="B116" s="21" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C116" s="21" t="s">
         <v>527</v>
@@ -19912,10 +19942,10 @@
     </row>
     <row r="117" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A117" s="21">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B117" s="21" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C117" s="21" t="s">
         <v>527</v>
@@ -19928,10 +19958,10 @@
     </row>
     <row r="118" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A118" s="21">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="B118" s="21" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C118" s="21" t="s">
         <v>527</v>
@@ -19944,10 +19974,10 @@
     </row>
     <row r="119" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A119" s="21">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B119" s="21" t="s">
-        <v>81</v>
+        <v>77</v>
       </c>
       <c r="C119" s="21" t="s">
         <v>527</v>
@@ -19960,65 +19990,57 @@
     </row>
     <row r="120" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A120" s="21">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B120" s="21" t="s">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="C120" s="21" t="s">
-        <v>525</v>
-      </c>
-      <c r="D120" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="E120" s="21" t="s">
-        <v>412</v>
-      </c>
-      <c r="F120" s="21" t="s">
-        <v>458</v>
-      </c>
+        <v>527</v>
+      </c>
+      <c r="D120" s="27"/>
+      <c r="E120" s="21"/>
+      <c r="F120" s="21"/>
       <c r="G120" s="24"/>
       <c r="H120" s="22"/>
     </row>
-    <row r="121" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A121" s="16">
+    <row r="121" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A121" s="21">
+        <v>46</v>
+      </c>
+      <c r="B121" s="21" t="s">
+        <v>81</v>
+      </c>
+      <c r="C121" s="21" t="s">
+        <v>527</v>
+      </c>
+      <c r="D121" s="27"/>
+      <c r="E121" s="21"/>
+      <c r="F121" s="21"/>
+      <c r="G121" s="24"/>
+      <c r="H121" s="22"/>
+    </row>
+    <row r="122" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A122" s="21">
         <v>47</v>
       </c>
-      <c r="B121" s="16" t="s">
+      <c r="B122" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="C121" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D121" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E121" s="16" t="s">
-        <v>460</v>
-      </c>
-      <c r="F121" s="16" t="s">
-        <v>459</v>
-      </c>
-    </row>
-    <row r="122" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A122" s="16">
-        <v>47</v>
-      </c>
-      <c r="B122" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="C122" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D122" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E122" s="16" t="s">
-        <v>462</v>
-      </c>
-      <c r="F122" s="16" t="s">
-        <v>461</v>
-      </c>
+      <c r="C122" s="21" t="s">
+        <v>525</v>
+      </c>
+      <c r="D122" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="E122" s="21" t="s">
+        <v>412</v>
+      </c>
+      <c r="F122" s="21" t="s">
+        <v>458</v>
+      </c>
+      <c r="G122" s="24"/>
+      <c r="H122" s="22"/>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A123" s="16">
@@ -20034,10 +20056,10 @@
         <v>0</v>
       </c>
       <c r="E123" s="16" t="s">
-        <v>464</v>
+        <v>460</v>
       </c>
       <c r="F123" s="16" t="s">
-        <v>463</v>
+        <v>459</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.25">
@@ -20054,10 +20076,10 @@
         <v>0</v>
       </c>
       <c r="E124" s="16" t="s">
-        <v>445</v>
+        <v>462</v>
       </c>
       <c r="F124" s="16" t="s">
-        <v>465</v>
+        <v>461</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.25">
@@ -20074,10 +20096,10 @@
         <v>0</v>
       </c>
       <c r="E125" s="16" t="s">
-        <v>467</v>
+        <v>464</v>
       </c>
       <c r="F125" s="16" t="s">
-        <v>466</v>
+        <v>463</v>
       </c>
     </row>
     <row r="126" spans="1:8" x14ac:dyDescent="0.25">
@@ -20094,76 +20116,76 @@
         <v>0</v>
       </c>
       <c r="E126" s="16" t="s">
-        <v>414</v>
+        <v>445</v>
       </c>
       <c r="F126" s="16" t="s">
-        <v>406</v>
-      </c>
-      <c r="H126" t="s">
-        <v>569</v>
-      </c>
-    </row>
-    <row r="127" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="21">
-        <v>48</v>
-      </c>
-      <c r="B127" s="21" t="s">
-        <v>85</v>
-      </c>
-      <c r="C127" s="21" t="s">
-        <v>525</v>
-      </c>
-      <c r="D127" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="E127" s="23" t="s">
-        <v>462</v>
-      </c>
-      <c r="F127" s="21" t="s">
-        <v>468</v>
-      </c>
-      <c r="G127" s="24"/>
-      <c r="H127" s="22"/>
+        <v>465</v>
+      </c>
+    </row>
+    <row r="127" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A127" s="16">
+        <v>47</v>
+      </c>
+      <c r="B127" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C127" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D127" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E127" s="16" t="s">
+        <v>467</v>
+      </c>
+      <c r="F127" s="16" t="s">
+        <v>466</v>
+      </c>
     </row>
     <row r="128" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A128" s="16">
+        <v>47</v>
+      </c>
+      <c r="B128" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C128" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D128" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E128" s="16" t="s">
+        <v>414</v>
+      </c>
+      <c r="F128" s="16" t="s">
+        <v>406</v>
+      </c>
+      <c r="H128" t="s">
+        <v>569</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A129" s="21">
         <v>48</v>
       </c>
-      <c r="B128" s="16" t="s">
+      <c r="B129" s="21" t="s">
         <v>85</v>
       </c>
-      <c r="C128" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D128" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E128" s="7" t="s">
-        <v>469</v>
-      </c>
-      <c r="F128" s="16" t="s">
-        <v>238</v>
-      </c>
-    </row>
-    <row r="129" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A129" s="16">
-        <v>48</v>
-      </c>
-      <c r="B129" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="C129" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D129" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E129" s="7" t="s">
-        <v>467</v>
-      </c>
-      <c r="F129" s="16" t="s">
-        <v>475</v>
-      </c>
+      <c r="C129" s="21" t="s">
+        <v>525</v>
+      </c>
+      <c r="D129" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="E129" s="23" t="s">
+        <v>462</v>
+      </c>
+      <c r="F129" s="21" t="s">
+        <v>468</v>
+      </c>
+      <c r="G129" s="24"/>
+      <c r="H129" s="22"/>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A130" s="16">
@@ -20179,10 +20201,10 @@
         <v>0</v>
       </c>
       <c r="E130" s="7" t="s">
-        <v>449</v>
+        <v>469</v>
       </c>
       <c r="F130" s="16" t="s">
-        <v>470</v>
+        <v>238</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.25">
@@ -20199,10 +20221,10 @@
         <v>0</v>
       </c>
       <c r="E131" s="7" t="s">
-        <v>472</v>
+        <v>467</v>
       </c>
       <c r="F131" s="16" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.25">
@@ -20219,10 +20241,10 @@
         <v>0</v>
       </c>
       <c r="E132" s="7" t="s">
-        <v>460</v>
+        <v>449</v>
       </c>
       <c r="F132" s="16" t="s">
-        <v>474</v>
+        <v>470</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.25">
@@ -20239,96 +20261,100 @@
         <v>0</v>
       </c>
       <c r="E133" s="7" t="s">
-        <v>414</v>
+        <v>472</v>
       </c>
       <c r="F133" s="16" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="134" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A134" s="21">
-        <v>49</v>
-      </c>
-      <c r="B134" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="C134" s="21" t="s">
-        <v>525</v>
-      </c>
-      <c r="D134" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="E134" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="F134" s="21" t="s">
-        <v>408</v>
-      </c>
-      <c r="G134" s="24"/>
-      <c r="H134" s="22"/>
+        <v>471</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A134" s="16">
+        <v>48</v>
+      </c>
+      <c r="B134" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="C134" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D134" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E134" s="7" t="s">
+        <v>460</v>
+      </c>
+      <c r="F134" s="16" t="s">
+        <v>474</v>
+      </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A135" s="16">
+        <v>48</v>
+      </c>
+      <c r="B135" s="16" t="s">
+        <v>85</v>
+      </c>
+      <c r="C135" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D135" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E135" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="F135" s="16" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A136" s="21">
         <v>49</v>
       </c>
-      <c r="B135" s="16" t="s">
+      <c r="B136" s="21" t="s">
         <v>87</v>
       </c>
-      <c r="C135" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D135" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E135" s="16" t="s">
+      <c r="C136" s="21" t="s">
+        <v>525</v>
+      </c>
+      <c r="D136" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="E136" s="21" t="s">
+        <v>409</v>
+      </c>
+      <c r="F136" s="21" t="s">
+        <v>408</v>
+      </c>
+      <c r="G136" s="24"/>
+      <c r="H136" s="22"/>
+    </row>
+    <row r="137" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A137" s="16">
+        <v>49</v>
+      </c>
+      <c r="B137" s="16" t="s">
+        <v>87</v>
+      </c>
+      <c r="C137" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D137" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E137" s="16" t="s">
         <v>412</v>
       </c>
-      <c r="F135" s="16" t="s">
+      <c r="F137" s="16" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="136" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A136" s="16">
-        <v>49</v>
-      </c>
-      <c r="B136" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="C136" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D136" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E136" s="16" t="s">
-        <v>414</v>
-      </c>
-      <c r="F136" s="16" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="137" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A137" s="21">
-        <v>50</v>
-      </c>
-      <c r="B137" s="21" t="s">
-        <v>89</v>
-      </c>
-      <c r="C137" s="21" t="s">
-        <v>527</v>
-      </c>
-      <c r="D137" s="27"/>
-      <c r="E137" s="21"/>
-      <c r="F137" s="21"/>
-      <c r="G137" s="24"/>
-      <c r="H137" s="22"/>
     </row>
     <row r="138" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A138" s="16">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="B138" s="16" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="C138" s="16" t="s">
         <v>525</v>
@@ -20336,32 +20362,28 @@
       <c r="D138" s="28" t="b">
         <v>0</v>
       </c>
-      <c r="E138" s="16">
-        <v>0</v>
+      <c r="E138" s="16" t="s">
+        <v>414</v>
       </c>
       <c r="F138" s="16" t="s">
-        <v>560</v>
-      </c>
-    </row>
-    <row r="139" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A139" s="16">
-        <v>51</v>
-      </c>
-      <c r="B139" s="16" t="s">
-        <v>91</v>
-      </c>
-      <c r="C139" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D139" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E139" s="16">
-        <v>1</v>
-      </c>
-      <c r="F139" s="16" t="s">
-        <v>570</v>
-      </c>
+        <v>406</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A139" s="21">
+        <v>50</v>
+      </c>
+      <c r="B139" s="21" t="s">
+        <v>89</v>
+      </c>
+      <c r="C139" s="21" t="s">
+        <v>527</v>
+      </c>
+      <c r="D139" s="27"/>
+      <c r="E139" s="21"/>
+      <c r="F139" s="21"/>
+      <c r="G139" s="24"/>
+      <c r="H139" s="22"/>
     </row>
     <row r="140" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A140" s="16">
@@ -20377,10 +20399,10 @@
         <v>0</v>
       </c>
       <c r="E140" s="16">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F140" s="16" t="s">
-        <v>571</v>
+        <v>560</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.25">
@@ -20397,10 +20419,10 @@
         <v>0</v>
       </c>
       <c r="E141" s="16">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F141" s="16" t="s">
-        <v>572</v>
+        <v>570</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.25">
@@ -20417,10 +20439,10 @@
         <v>0</v>
       </c>
       <c r="E142" s="16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F142" s="16" t="s">
-        <v>573</v>
+        <v>571</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.25">
@@ -20437,10 +20459,10 @@
         <v>0</v>
       </c>
       <c r="E143" s="16">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="F143" s="16" t="s">
-        <v>574</v>
+        <v>572</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.25">
@@ -20457,10 +20479,10 @@
         <v>0</v>
       </c>
       <c r="E144" s="16">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F144" s="16" t="s">
-        <v>575</v>
+        <v>573</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.25">
@@ -20477,10 +20499,10 @@
         <v>0</v>
       </c>
       <c r="E145" s="16">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F145" s="16" t="s">
-        <v>576</v>
+        <v>574</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.25">
@@ -20497,10 +20519,10 @@
         <v>0</v>
       </c>
       <c r="E146" s="16">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F146" s="16" t="s">
-        <v>577</v>
+        <v>575</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.25">
@@ -20517,73 +20539,73 @@
         <v>0</v>
       </c>
       <c r="E147" s="16">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="F147" s="16" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="148" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A148" s="21">
-        <v>52</v>
-      </c>
-      <c r="B148" s="21" t="s">
-        <v>93</v>
-      </c>
-      <c r="C148" s="21" t="s">
-        <v>525</v>
-      </c>
-      <c r="D148" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="E148" s="21">
-        <v>1</v>
-      </c>
-      <c r="F148" s="21" t="s">
-        <v>578</v>
-      </c>
-      <c r="G148" s="24"/>
-      <c r="H148" s="22"/>
+        <v>576</v>
+      </c>
+    </row>
+    <row r="148" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A148" s="16">
+        <v>51</v>
+      </c>
+      <c r="B148" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="C148" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D148" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E148" s="16">
+        <v>8</v>
+      </c>
+      <c r="F148" s="16" t="s">
+        <v>577</v>
+      </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A149" s="16">
+        <v>51</v>
+      </c>
+      <c r="B149" s="16" t="s">
+        <v>91</v>
+      </c>
+      <c r="C149" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D149" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E149" s="16">
+        <v>9</v>
+      </c>
+      <c r="F149" s="16" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="150" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A150" s="21">
         <v>52</v>
       </c>
-      <c r="B149" s="16" t="s">
+      <c r="B150" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="C149" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D149" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E149" s="16">
-        <v>2</v>
-      </c>
-      <c r="F149" s="16" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="150" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A150" s="16">
-        <v>52</v>
-      </c>
-      <c r="B150" s="16" t="s">
-        <v>93</v>
-      </c>
-      <c r="C150" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D150" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E150" s="16">
-        <v>3</v>
-      </c>
-      <c r="F150" s="16" t="s">
-        <v>580</v>
-      </c>
+      <c r="C150" s="21" t="s">
+        <v>525</v>
+      </c>
+      <c r="D150" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="E150" s="21">
+        <v>1</v>
+      </c>
+      <c r="F150" s="21" t="s">
+        <v>578</v>
+      </c>
+      <c r="G150" s="24"/>
+      <c r="H150" s="22"/>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A151" s="16">
@@ -20599,10 +20621,10 @@
         <v>0</v>
       </c>
       <c r="E151" s="16">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F151" s="16" t="s">
-        <v>581</v>
+        <v>579</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.25">
@@ -20619,10 +20641,10 @@
         <v>0</v>
       </c>
       <c r="E152" s="16">
-        <v>8</v>
+        <v>3</v>
       </c>
       <c r="F152" s="16" t="s">
-        <v>582</v>
+        <v>580</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.25">
@@ -20639,879 +20661,879 @@
         <v>0</v>
       </c>
       <c r="E153" s="16">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F153" s="16" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="154" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A154" s="21">
-        <v>53</v>
-      </c>
-      <c r="B154" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="C154" s="21" t="s">
-        <v>525</v>
-      </c>
-      <c r="D154" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="E154" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="F154" s="21" t="s">
-        <v>408</v>
-      </c>
-      <c r="G154" s="24"/>
-      <c r="H154" s="22"/>
+        <v>581</v>
+      </c>
+    </row>
+    <row r="154" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A154" s="16">
+        <v>52</v>
+      </c>
+      <c r="B154" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="C154" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D154" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E154" s="16">
+        <v>8</v>
+      </c>
+      <c r="F154" s="16" t="s">
+        <v>582</v>
+      </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A155" s="16">
+        <v>52</v>
+      </c>
+      <c r="B155" s="16" t="s">
+        <v>93</v>
+      </c>
+      <c r="C155" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D155" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E155" s="16">
+        <v>9</v>
+      </c>
+      <c r="F155" s="16" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="156" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A156" s="21">
         <v>53</v>
       </c>
-      <c r="B155" s="16" t="s">
+      <c r="B156" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="C155" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D155" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E155" s="16" t="s">
+      <c r="C156" s="21" t="s">
+        <v>525</v>
+      </c>
+      <c r="D156" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="E156" s="21" t="s">
+        <v>409</v>
+      </c>
+      <c r="F156" s="21" t="s">
+        <v>408</v>
+      </c>
+      <c r="G156" s="24"/>
+      <c r="H156" s="22"/>
+    </row>
+    <row r="157" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A157" s="16">
+        <v>53</v>
+      </c>
+      <c r="B157" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="C157" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D157" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E157" s="16" t="s">
         <v>412</v>
       </c>
-      <c r="F155" s="16" t="s">
+      <c r="F157" s="16" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="156" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A156" s="16">
-        <v>53</v>
-      </c>
-      <c r="B156" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="C156" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D156" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E156" s="16" t="s">
-        <v>414</v>
-      </c>
-      <c r="F156" s="16" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="157" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A157" s="21">
-        <v>54</v>
-      </c>
-      <c r="B157" s="21" t="s">
-        <v>97</v>
-      </c>
-      <c r="C157" s="21" t="s">
-        <v>525</v>
-      </c>
-      <c r="D157" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="E157" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="F157" s="21" t="s">
-        <v>408</v>
-      </c>
-      <c r="G157" s="24"/>
-      <c r="H157" s="22"/>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A158" s="16">
+        <v>53</v>
+      </c>
+      <c r="B158" s="16" t="s">
+        <v>95</v>
+      </c>
+      <c r="C158" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D158" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E158" s="16" t="s">
+        <v>414</v>
+      </c>
+      <c r="F158" s="16" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="159" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A159" s="21">
         <v>54</v>
       </c>
-      <c r="B158" s="16" t="s">
+      <c r="B159" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="C158" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D158" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E158" s="16" t="s">
+      <c r="C159" s="21" t="s">
+        <v>525</v>
+      </c>
+      <c r="D159" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="E159" s="21" t="s">
+        <v>409</v>
+      </c>
+      <c r="F159" s="21" t="s">
+        <v>408</v>
+      </c>
+      <c r="G159" s="24"/>
+      <c r="H159" s="22"/>
+    </row>
+    <row r="160" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A160" s="16">
+        <v>54</v>
+      </c>
+      <c r="B160" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="C160" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D160" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E160" s="16" t="s">
         <v>412</v>
       </c>
-      <c r="F158" s="16" t="s">
+      <c r="F160" s="16" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="159" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A159" s="16">
-        <v>54</v>
-      </c>
-      <c r="B159" s="16" t="s">
-        <v>97</v>
-      </c>
-      <c r="C159" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D159" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E159" s="16" t="s">
-        <v>414</v>
-      </c>
-      <c r="F159" s="16" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="160" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A160" s="21">
-        <v>55</v>
-      </c>
-      <c r="B160" s="21" t="s">
-        <v>99</v>
-      </c>
-      <c r="C160" s="21" t="s">
-        <v>525</v>
-      </c>
-      <c r="D160" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="E160" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="F160" s="21" t="s">
-        <v>408</v>
-      </c>
-      <c r="G160" s="24"/>
-      <c r="H160" s="22"/>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A161" s="16">
+        <v>54</v>
+      </c>
+      <c r="B161" s="16" t="s">
+        <v>97</v>
+      </c>
+      <c r="C161" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D161" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E161" s="16" t="s">
+        <v>414</v>
+      </c>
+      <c r="F161" s="16" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="162" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A162" s="21">
         <v>55</v>
       </c>
-      <c r="B161" s="16" t="s">
+      <c r="B162" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="C161" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D161" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E161" s="16" t="s">
+      <c r="C162" s="21" t="s">
+        <v>525</v>
+      </c>
+      <c r="D162" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="E162" s="21" t="s">
+        <v>409</v>
+      </c>
+      <c r="F162" s="21" t="s">
+        <v>408</v>
+      </c>
+      <c r="G162" s="24"/>
+      <c r="H162" s="22"/>
+    </row>
+    <row r="163" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A163" s="16">
+        <v>55</v>
+      </c>
+      <c r="B163" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="C163" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D163" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E163" s="16" t="s">
         <v>412</v>
       </c>
-      <c r="F161" s="16" t="s">
+      <c r="F163" s="16" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="162" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A162" s="16">
-        <v>55</v>
-      </c>
-      <c r="B162" s="16" t="s">
-        <v>99</v>
-      </c>
-      <c r="C162" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D162" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E162" s="16" t="s">
-        <v>414</v>
-      </c>
-      <c r="F162" s="16" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="163" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A163" s="21">
-        <v>56</v>
-      </c>
-      <c r="B163" s="21" t="s">
-        <v>101</v>
-      </c>
-      <c r="C163" s="21" t="s">
-        <v>525</v>
-      </c>
-      <c r="D163" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="E163" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="F163" s="21" t="s">
-        <v>408</v>
-      </c>
-      <c r="G163" s="24"/>
-      <c r="H163" s="22"/>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A164" s="16">
+        <v>55</v>
+      </c>
+      <c r="B164" s="16" t="s">
+        <v>99</v>
+      </c>
+      <c r="C164" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D164" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E164" s="16" t="s">
+        <v>414</v>
+      </c>
+      <c r="F164" s="16" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="165" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A165" s="21">
         <v>56</v>
       </c>
-      <c r="B164" s="16" t="s">
+      <c r="B165" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="C164" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D164" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E164" s="16" t="s">
+      <c r="C165" s="21" t="s">
+        <v>525</v>
+      </c>
+      <c r="D165" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="E165" s="21" t="s">
+        <v>409</v>
+      </c>
+      <c r="F165" s="21" t="s">
+        <v>408</v>
+      </c>
+      <c r="G165" s="24"/>
+      <c r="H165" s="22"/>
+    </row>
+    <row r="166" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A166" s="16">
+        <v>56</v>
+      </c>
+      <c r="B166" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="C166" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D166" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E166" s="16" t="s">
         <v>412</v>
       </c>
-      <c r="F164" s="16" t="s">
+      <c r="F166" s="16" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="165" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A165" s="16">
-        <v>56</v>
-      </c>
-      <c r="B165" s="16" t="s">
-        <v>101</v>
-      </c>
-      <c r="C165" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D165" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E165" s="16" t="s">
-        <v>414</v>
-      </c>
-      <c r="F165" s="16" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="166" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A166" s="21">
-        <v>57</v>
-      </c>
-      <c r="B166" s="21" t="s">
-        <v>103</v>
-      </c>
-      <c r="C166" s="21" t="s">
-        <v>525</v>
-      </c>
-      <c r="D166" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="E166" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="F166" s="21" t="s">
-        <v>408</v>
-      </c>
-      <c r="G166" s="24"/>
-      <c r="H166" s="22"/>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A167" s="16">
+        <v>56</v>
+      </c>
+      <c r="B167" s="16" t="s">
+        <v>101</v>
+      </c>
+      <c r="C167" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D167" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E167" s="16" t="s">
+        <v>414</v>
+      </c>
+      <c r="F167" s="16" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="168" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A168" s="21">
         <v>57</v>
       </c>
-      <c r="B167" s="16" t="s">
+      <c r="B168" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="C167" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D167" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E167" s="16" t="s">
+      <c r="C168" s="21" t="s">
+        <v>525</v>
+      </c>
+      <c r="D168" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="E168" s="21" t="s">
+        <v>409</v>
+      </c>
+      <c r="F168" s="21" t="s">
+        <v>408</v>
+      </c>
+      <c r="G168" s="24"/>
+      <c r="H168" s="22"/>
+    </row>
+    <row r="169" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A169" s="16">
+        <v>57</v>
+      </c>
+      <c r="B169" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="C169" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D169" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E169" s="16" t="s">
         <v>412</v>
       </c>
-      <c r="F167" s="16" t="s">
+      <c r="F169" s="16" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="168" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A168" s="16">
-        <v>57</v>
-      </c>
-      <c r="B168" s="16" t="s">
-        <v>103</v>
-      </c>
-      <c r="C168" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D168" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E168" s="16" t="s">
-        <v>414</v>
-      </c>
-      <c r="F168" s="16" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="169" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A169" s="21">
-        <v>58</v>
-      </c>
-      <c r="B169" s="21" t="s">
-        <v>105</v>
-      </c>
-      <c r="C169" s="21" t="s">
-        <v>525</v>
-      </c>
-      <c r="D169" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="E169" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="F169" s="21" t="s">
-        <v>408</v>
-      </c>
-      <c r="G169" s="24"/>
-      <c r="H169" s="22"/>
     </row>
     <row r="170" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A170" s="16">
+        <v>57</v>
+      </c>
+      <c r="B170" s="16" t="s">
+        <v>103</v>
+      </c>
+      <c r="C170" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D170" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E170" s="16" t="s">
+        <v>414</v>
+      </c>
+      <c r="F170" s="16" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="171" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A171" s="21">
         <v>58</v>
       </c>
-      <c r="B170" s="16" t="s">
+      <c r="B171" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="C170" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D170" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E170" s="16" t="s">
+      <c r="C171" s="21" t="s">
+        <v>525</v>
+      </c>
+      <c r="D171" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="E171" s="21" t="s">
+        <v>409</v>
+      </c>
+      <c r="F171" s="21" t="s">
+        <v>408</v>
+      </c>
+      <c r="G171" s="24"/>
+      <c r="H171" s="22"/>
+    </row>
+    <row r="172" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A172" s="16">
+        <v>58</v>
+      </c>
+      <c r="B172" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="C172" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D172" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E172" s="16" t="s">
         <v>412</v>
       </c>
-      <c r="F170" s="16" t="s">
+      <c r="F172" s="16" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="171" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A171" s="16">
-        <v>58</v>
-      </c>
-      <c r="B171" s="16" t="s">
-        <v>105</v>
-      </c>
-      <c r="C171" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D171" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E171" s="16" t="s">
-        <v>414</v>
-      </c>
-      <c r="F171" s="16" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="172" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A172" s="21">
-        <v>59</v>
-      </c>
-      <c r="B172" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="C172" s="21" t="s">
-        <v>525</v>
-      </c>
-      <c r="D172" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="E172" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="F172" s="21" t="s">
-        <v>408</v>
-      </c>
-      <c r="G172" s="24"/>
-      <c r="H172" s="22"/>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A173" s="16">
+        <v>58</v>
+      </c>
+      <c r="B173" s="16" t="s">
+        <v>105</v>
+      </c>
+      <c r="C173" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D173" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E173" s="16" t="s">
+        <v>414</v>
+      </c>
+      <c r="F173" s="16" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="174" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A174" s="21">
         <v>59</v>
       </c>
-      <c r="B173" s="16" t="s">
+      <c r="B174" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="C173" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D173" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E173" s="16" t="s">
+      <c r="C174" s="21" t="s">
+        <v>525</v>
+      </c>
+      <c r="D174" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="E174" s="21" t="s">
+        <v>409</v>
+      </c>
+      <c r="F174" s="21" t="s">
+        <v>408</v>
+      </c>
+      <c r="G174" s="24"/>
+      <c r="H174" s="22"/>
+    </row>
+    <row r="175" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A175" s="16">
+        <v>59</v>
+      </c>
+      <c r="B175" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="C175" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D175" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E175" s="16" t="s">
         <v>412</v>
       </c>
-      <c r="F173" s="16" t="s">
+      <c r="F175" s="16" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="174" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A174" s="16">
-        <v>59</v>
-      </c>
-      <c r="B174" s="16" t="s">
-        <v>107</v>
-      </c>
-      <c r="C174" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D174" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E174" s="16" t="s">
-        <v>414</v>
-      </c>
-      <c r="F174" s="16" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="175" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A175" s="21">
-        <v>60</v>
-      </c>
-      <c r="B175" s="21" t="s">
-        <v>109</v>
-      </c>
-      <c r="C175" s="21" t="s">
-        <v>525</v>
-      </c>
-      <c r="D175" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="E175" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="F175" s="21" t="s">
-        <v>408</v>
-      </c>
-      <c r="G175" s="24"/>
-      <c r="H175" s="22"/>
     </row>
     <row r="176" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A176" s="16">
+        <v>59</v>
+      </c>
+      <c r="B176" s="16" t="s">
+        <v>107</v>
+      </c>
+      <c r="C176" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D176" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E176" s="16" t="s">
+        <v>414</v>
+      </c>
+      <c r="F176" s="16" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="177" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A177" s="21">
         <v>60</v>
       </c>
-      <c r="B176" s="16" t="s">
+      <c r="B177" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="C176" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D176" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E176" s="16" t="s">
+      <c r="C177" s="21" t="s">
+        <v>525</v>
+      </c>
+      <c r="D177" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="E177" s="21" t="s">
+        <v>409</v>
+      </c>
+      <c r="F177" s="21" t="s">
+        <v>408</v>
+      </c>
+      <c r="G177" s="24"/>
+      <c r="H177" s="22"/>
+    </row>
+    <row r="178" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A178" s="16">
+        <v>60</v>
+      </c>
+      <c r="B178" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="C178" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D178" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E178" s="16" t="s">
         <v>412</v>
       </c>
-      <c r="F176" s="16" t="s">
+      <c r="F178" s="16" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="177" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A177" s="16">
-        <v>60</v>
-      </c>
-      <c r="B177" s="16" t="s">
-        <v>109</v>
-      </c>
-      <c r="C177" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D177" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E177" s="16" t="s">
-        <v>414</v>
-      </c>
-      <c r="F177" s="16" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="178" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A178" s="21">
-        <v>61</v>
-      </c>
-      <c r="B178" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="C178" s="21" t="s">
-        <v>525</v>
-      </c>
-      <c r="D178" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="E178" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="F178" s="21" t="s">
-        <v>408</v>
-      </c>
-      <c r="G178" s="24"/>
-      <c r="H178" s="22"/>
     </row>
     <row r="179" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A179" s="16">
+        <v>60</v>
+      </c>
+      <c r="B179" s="16" t="s">
+        <v>109</v>
+      </c>
+      <c r="C179" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D179" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E179" s="16" t="s">
+        <v>414</v>
+      </c>
+      <c r="F179" s="16" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="180" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A180" s="21">
         <v>61</v>
       </c>
-      <c r="B179" s="16" t="s">
+      <c r="B180" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="C179" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D179" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E179" s="16" t="s">
+      <c r="C180" s="21" t="s">
+        <v>525</v>
+      </c>
+      <c r="D180" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="E180" s="21" t="s">
+        <v>409</v>
+      </c>
+      <c r="F180" s="21" t="s">
+        <v>408</v>
+      </c>
+      <c r="G180" s="24"/>
+      <c r="H180" s="22"/>
+    </row>
+    <row r="181" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A181" s="16">
+        <v>61</v>
+      </c>
+      <c r="B181" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="C181" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D181" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E181" s="16" t="s">
         <v>412</v>
       </c>
-      <c r="F179" s="16" t="s">
+      <c r="F181" s="16" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="180" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A180" s="16">
-        <v>61</v>
-      </c>
-      <c r="B180" s="16" t="s">
-        <v>111</v>
-      </c>
-      <c r="C180" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D180" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E180" s="16" t="s">
-        <v>414</v>
-      </c>
-      <c r="F180" s="16" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="181" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A181" s="21">
-        <v>62</v>
-      </c>
-      <c r="B181" s="21" t="s">
-        <v>113</v>
-      </c>
-      <c r="C181" s="21" t="s">
-        <v>525</v>
-      </c>
-      <c r="D181" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="E181" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="F181" s="21" t="s">
-        <v>408</v>
-      </c>
-      <c r="G181" s="24"/>
-      <c r="H181" s="22"/>
     </row>
     <row r="182" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A182" s="16">
+        <v>61</v>
+      </c>
+      <c r="B182" s="16" t="s">
+        <v>111</v>
+      </c>
+      <c r="C182" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D182" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E182" s="16" t="s">
+        <v>414</v>
+      </c>
+      <c r="F182" s="16" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="183" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A183" s="21">
         <v>62</v>
       </c>
-      <c r="B182" s="16" t="s">
+      <c r="B183" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="C182" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D182" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E182" s="16" t="s">
+      <c r="C183" s="21" t="s">
+        <v>525</v>
+      </c>
+      <c r="D183" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="E183" s="21" t="s">
+        <v>409</v>
+      </c>
+      <c r="F183" s="21" t="s">
+        <v>408</v>
+      </c>
+      <c r="G183" s="24"/>
+      <c r="H183" s="22"/>
+    </row>
+    <row r="184" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A184" s="16">
+        <v>62</v>
+      </c>
+      <c r="B184" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="C184" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D184" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E184" s="16" t="s">
         <v>412</v>
       </c>
-      <c r="F182" s="16" t="s">
+      <c r="F184" s="16" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="183" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A183" s="16">
-        <v>62</v>
-      </c>
-      <c r="B183" s="16" t="s">
-        <v>113</v>
-      </c>
-      <c r="C183" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D183" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E183" s="16" t="s">
-        <v>414</v>
-      </c>
-      <c r="F183" s="16" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="184" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A184" s="21">
-        <v>63</v>
-      </c>
-      <c r="B184" s="21" t="s">
-        <v>115</v>
-      </c>
-      <c r="C184" s="21" t="s">
-        <v>525</v>
-      </c>
-      <c r="D184" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="E184" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="F184" s="21" t="s">
-        <v>408</v>
-      </c>
-      <c r="G184" s="24"/>
-      <c r="H184" s="22"/>
     </row>
     <row r="185" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A185" s="16">
+        <v>62</v>
+      </c>
+      <c r="B185" s="16" t="s">
+        <v>113</v>
+      </c>
+      <c r="C185" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D185" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E185" s="16" t="s">
+        <v>414</v>
+      </c>
+      <c r="F185" s="16" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="186" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A186" s="21">
         <v>63</v>
       </c>
-      <c r="B185" s="16" t="s">
+      <c r="B186" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="C185" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D185" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E185" s="16" t="s">
+      <c r="C186" s="21" t="s">
+        <v>525</v>
+      </c>
+      <c r="D186" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="E186" s="21" t="s">
+        <v>409</v>
+      </c>
+      <c r="F186" s="21" t="s">
+        <v>408</v>
+      </c>
+      <c r="G186" s="24"/>
+      <c r="H186" s="22"/>
+    </row>
+    <row r="187" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A187" s="16">
+        <v>63</v>
+      </c>
+      <c r="B187" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="C187" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D187" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E187" s="16" t="s">
         <v>412</v>
       </c>
-      <c r="F185" s="16" t="s">
+      <c r="F187" s="16" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="186" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A186" s="16">
-        <v>63</v>
-      </c>
-      <c r="B186" s="16" t="s">
-        <v>115</v>
-      </c>
-      <c r="C186" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D186" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E186" s="16" t="s">
-        <v>414</v>
-      </c>
-      <c r="F186" s="16" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="187" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A187" s="21">
-        <v>64</v>
-      </c>
-      <c r="B187" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="C187" s="21" t="s">
-        <v>525</v>
-      </c>
-      <c r="D187" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="E187" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="F187" s="21" t="s">
-        <v>408</v>
-      </c>
-      <c r="G187" s="24"/>
-      <c r="H187" s="22"/>
     </row>
     <row r="188" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A188" s="16">
+        <v>63</v>
+      </c>
+      <c r="B188" s="16" t="s">
+        <v>115</v>
+      </c>
+      <c r="C188" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D188" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E188" s="16" t="s">
+        <v>414</v>
+      </c>
+      <c r="F188" s="16" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="189" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A189" s="21">
         <v>64</v>
       </c>
-      <c r="B188" s="16" t="s">
+      <c r="B189" s="21" t="s">
         <v>117</v>
       </c>
-      <c r="C188" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D188" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E188" s="16" t="s">
+      <c r="C189" s="21" t="s">
+        <v>525</v>
+      </c>
+      <c r="D189" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="E189" s="21" t="s">
+        <v>409</v>
+      </c>
+      <c r="F189" s="21" t="s">
+        <v>408</v>
+      </c>
+      <c r="G189" s="24"/>
+      <c r="H189" s="22"/>
+    </row>
+    <row r="190" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A190" s="16">
+        <v>64</v>
+      </c>
+      <c r="B190" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="C190" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D190" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E190" s="16" t="s">
         <v>412</v>
       </c>
-      <c r="F188" s="16" t="s">
+      <c r="F190" s="16" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="189" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A189" s="16">
-        <v>64</v>
-      </c>
-      <c r="B189" s="16" t="s">
-        <v>117</v>
-      </c>
-      <c r="C189" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D189" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E189" s="16" t="s">
-        <v>414</v>
-      </c>
-      <c r="F189" s="16" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="190" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A190" s="21">
-        <v>65</v>
-      </c>
-      <c r="B190" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="C190" s="21" t="s">
-        <v>525</v>
-      </c>
-      <c r="D190" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="E190" s="21" t="s">
-        <v>409</v>
-      </c>
-      <c r="F190" s="21" t="s">
-        <v>408</v>
-      </c>
-      <c r="G190" s="24"/>
-      <c r="H190" s="22"/>
     </row>
     <row r="191" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A191" s="16">
+        <v>64</v>
+      </c>
+      <c r="B191" s="16" t="s">
+        <v>117</v>
+      </c>
+      <c r="C191" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D191" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E191" s="16" t="s">
+        <v>414</v>
+      </c>
+      <c r="F191" s="16" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="192" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A192" s="21">
         <v>65</v>
       </c>
-      <c r="B191" s="16" t="s">
+      <c r="B192" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="C191" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D191" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E191" s="16" t="s">
+      <c r="C192" s="21" t="s">
+        <v>525</v>
+      </c>
+      <c r="D192" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="E192" s="21" t="s">
+        <v>409</v>
+      </c>
+      <c r="F192" s="21" t="s">
+        <v>408</v>
+      </c>
+      <c r="G192" s="24"/>
+      <c r="H192" s="22"/>
+    </row>
+    <row r="193" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A193" s="16">
+        <v>65</v>
+      </c>
+      <c r="B193" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="C193" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D193" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E193" s="16" t="s">
         <v>412</v>
       </c>
-      <c r="F191" s="16" t="s">
+      <c r="F193" s="16" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="192" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A192" s="16">
-        <v>65</v>
-      </c>
-      <c r="B192" s="16" t="s">
-        <v>119</v>
-      </c>
-      <c r="C192" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D192" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E192" s="16" t="s">
-        <v>414</v>
-      </c>
-      <c r="F192" s="16" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="193" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A193" s="21">
-        <v>66</v>
-      </c>
-      <c r="B193" s="21" t="s">
-        <v>121</v>
-      </c>
-      <c r="C193" s="21" t="s">
-        <v>525</v>
-      </c>
-      <c r="D193" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="E193" s="21">
-        <v>10</v>
-      </c>
-      <c r="F193" s="21" t="s">
-        <v>583</v>
-      </c>
-      <c r="G193" s="24"/>
-      <c r="H193" s="22"/>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A194" s="16">
+        <v>65</v>
+      </c>
+      <c r="B194" s="16" t="s">
+        <v>119</v>
+      </c>
+      <c r="C194" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D194" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E194" s="16" t="s">
+        <v>414</v>
+      </c>
+      <c r="F194" s="16" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="195" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A195" s="21">
         <v>66</v>
       </c>
-      <c r="B194" s="16" t="s">
+      <c r="B195" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="C194" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D194" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E194" s="16">
-        <v>11</v>
-      </c>
-      <c r="F194" s="16" t="s">
-        <v>584</v>
-      </c>
-    </row>
-    <row r="195" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A195" s="16">
-        <v>66</v>
-      </c>
-      <c r="B195" s="16" t="s">
-        <v>121</v>
-      </c>
-      <c r="C195" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D195" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E195" s="16">
-        <v>12</v>
-      </c>
-      <c r="F195" s="16" t="s">
-        <v>585</v>
-      </c>
+      <c r="C195" s="21" t="s">
+        <v>525</v>
+      </c>
+      <c r="D195" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="E195" s="21">
+        <v>10</v>
+      </c>
+      <c r="F195" s="21" t="s">
+        <v>583</v>
+      </c>
+      <c r="G195" s="24"/>
+      <c r="H195" s="22"/>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A196" s="16">
@@ -21527,10 +21549,10 @@
         <v>0</v>
       </c>
       <c r="E196" s="16">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="F196" s="16" t="s">
-        <v>586</v>
+        <v>584</v>
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.25">
@@ -21547,10 +21569,10 @@
         <v>0</v>
       </c>
       <c r="E197" s="16">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F197" s="16" t="s">
-        <v>587</v>
+        <v>585</v>
       </c>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.25">
@@ -21567,10 +21589,10 @@
         <v>0</v>
       </c>
       <c r="E198" s="16">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="F198" s="16" t="s">
-        <v>588</v>
+        <v>586</v>
       </c>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.25">
@@ -21587,10 +21609,10 @@
         <v>0</v>
       </c>
       <c r="E199" s="16">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="F199" s="16" t="s">
-        <v>589</v>
+        <v>587</v>
       </c>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.25">
@@ -21607,10 +21629,10 @@
         <v>0</v>
       </c>
       <c r="E200" s="16">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="F200" s="16" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.25">
@@ -21627,10 +21649,10 @@
         <v>0</v>
       </c>
       <c r="E201" s="16">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F201" s="16" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.25">
@@ -21647,10 +21669,10 @@
         <v>0</v>
       </c>
       <c r="E202" s="16">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="F202" s="16" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.25">
@@ -21667,10 +21689,10 @@
         <v>0</v>
       </c>
       <c r="E203" s="16">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="F203" s="16" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.25">
@@ -21687,10 +21709,10 @@
         <v>0</v>
       </c>
       <c r="E204" s="16">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="F204" s="16" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.25">
@@ -21707,10 +21729,10 @@
         <v>0</v>
       </c>
       <c r="E205" s="16">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F205" s="16" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.25">
@@ -21727,10 +21749,10 @@
         <v>0</v>
       </c>
       <c r="E206" s="16">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="F206" s="16" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.25">
@@ -21747,10 +21769,10 @@
         <v>0</v>
       </c>
       <c r="E207" s="16">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="F207" s="16" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.25">
@@ -21767,10 +21789,10 @@
         <v>0</v>
       </c>
       <c r="E208" s="16">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="F208" s="16" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
     </row>
     <row r="209" spans="1:6" x14ac:dyDescent="0.25">
@@ -21787,10 +21809,10 @@
         <v>0</v>
       </c>
       <c r="E209" s="16">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="F209" s="16" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
     </row>
     <row r="210" spans="1:6" x14ac:dyDescent="0.25">
@@ -21807,10 +21829,10 @@
         <v>0</v>
       </c>
       <c r="E210" s="16">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="F210" s="16" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
     </row>
     <row r="211" spans="1:6" x14ac:dyDescent="0.25">
@@ -21827,13 +21849,13 @@
         <v>0</v>
       </c>
       <c r="E211" s="16">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="F211" s="16" t="s">
-        <v>601</v>
-      </c>
-    </row>
-    <row r="212" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="212" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A212" s="16">
         <v>66</v>
       </c>
@@ -21847,10 +21869,10 @@
         <v>0</v>
       </c>
       <c r="E212" s="16">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="F212" s="16" t="s">
-        <v>602</v>
+        <v>600</v>
       </c>
     </row>
     <row r="213" spans="1:6" x14ac:dyDescent="0.25">
@@ -21867,13 +21889,13 @@
         <v>0</v>
       </c>
       <c r="E213" s="16">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="F213" s="16" t="s">
-        <v>603</v>
-      </c>
-    </row>
-    <row r="214" spans="1:6" x14ac:dyDescent="0.25">
+        <v>601</v>
+      </c>
+    </row>
+    <row r="214" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A214" s="16">
         <v>66</v>
       </c>
@@ -21887,13 +21909,13 @@
         <v>0</v>
       </c>
       <c r="E214" s="16">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="F214" s="16" t="s">
-        <v>604</v>
-      </c>
-    </row>
-    <row r="215" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+        <v>602</v>
+      </c>
+    </row>
+    <row r="215" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A215" s="16">
         <v>66</v>
       </c>
@@ -21907,10 +21929,10 @@
         <v>0</v>
       </c>
       <c r="E215" s="16">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="F215" s="16" t="s">
-        <v>605</v>
+        <v>603</v>
       </c>
     </row>
     <row r="216" spans="1:6" x14ac:dyDescent="0.25">
@@ -21927,10 +21949,10 @@
         <v>0</v>
       </c>
       <c r="E216" s="16">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="F216" s="16" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
     </row>
     <row r="217" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -21947,10 +21969,10 @@
         <v>0</v>
       </c>
       <c r="E217" s="16">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F217" s="16" t="s">
-        <v>607</v>
+        <v>605</v>
       </c>
     </row>
     <row r="218" spans="1:6" x14ac:dyDescent="0.25">
@@ -21967,10 +21989,10 @@
         <v>0</v>
       </c>
       <c r="E218" s="16">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F218" s="16" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
     </row>
     <row r="219" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -21987,10 +22009,10 @@
         <v>0</v>
       </c>
       <c r="E219" s="16">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F219" s="16" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
     </row>
     <row r="220" spans="1:6" x14ac:dyDescent="0.25">
@@ -22007,10 +22029,10 @@
         <v>0</v>
       </c>
       <c r="E220" s="16">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F220" s="16" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
     </row>
     <row r="221" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -22027,13 +22049,13 @@
         <v>0</v>
       </c>
       <c r="E221" s="16">
-        <v>43</v>
+        <v>41</v>
       </c>
       <c r="F221" s="16" t="s">
-        <v>611</v>
-      </c>
-    </row>
-    <row r="222" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+        <v>609</v>
+      </c>
+    </row>
+    <row r="222" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A222" s="16">
         <v>66</v>
       </c>
@@ -22047,10 +22069,10 @@
         <v>0</v>
       </c>
       <c r="E222" s="16">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="F222" s="16" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
     </row>
     <row r="223" spans="1:6" ht="30" x14ac:dyDescent="0.25">
@@ -22067,13 +22089,13 @@
         <v>0</v>
       </c>
       <c r="E223" s="16">
-        <v>50</v>
+        <v>43</v>
       </c>
       <c r="F223" s="16" t="s">
-        <v>613</v>
-      </c>
-    </row>
-    <row r="224" spans="1:6" x14ac:dyDescent="0.25">
+        <v>611</v>
+      </c>
+    </row>
+    <row r="224" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A224" s="16">
         <v>66</v>
       </c>
@@ -22087,174 +22109,182 @@
         <v>0</v>
       </c>
       <c r="E224" s="16">
-        <v>99</v>
+        <v>44</v>
       </c>
       <c r="F224" s="16" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="225" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A225" s="21">
-        <v>67</v>
-      </c>
-      <c r="B225" s="23" t="s">
-        <v>123</v>
-      </c>
-      <c r="C225" s="23" t="s">
-        <v>525</v>
-      </c>
-      <c r="D225" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="E225" s="23" t="s">
-        <v>409</v>
-      </c>
-      <c r="F225" s="23" t="s">
-        <v>408</v>
-      </c>
-      <c r="G225" s="24"/>
-      <c r="H225" s="22"/>
+        <v>612</v>
+      </c>
+    </row>
+    <row r="225" spans="1:8" ht="30" x14ac:dyDescent="0.25">
+      <c r="A225" s="16">
+        <v>66</v>
+      </c>
+      <c r="B225" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="C225" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D225" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E225" s="16">
+        <v>50</v>
+      </c>
+      <c r="F225" s="16" t="s">
+        <v>613</v>
+      </c>
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A226" s="16">
+        <v>66</v>
+      </c>
+      <c r="B226" s="16" t="s">
+        <v>121</v>
+      </c>
+      <c r="C226" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D226" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E226" s="16">
+        <v>99</v>
+      </c>
+      <c r="F226" s="16" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="227" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A227" s="21">
         <v>67</v>
       </c>
-      <c r="B226" s="7" t="s">
+      <c r="B227" s="23" t="s">
         <v>123</v>
       </c>
-      <c r="C226" s="7" t="s">
-        <v>525</v>
-      </c>
-      <c r="D226" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E226" s="7" t="s">
+      <c r="C227" s="23" t="s">
+        <v>525</v>
+      </c>
+      <c r="D227" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="E227" s="23" t="s">
+        <v>409</v>
+      </c>
+      <c r="F227" s="23" t="s">
+        <v>408</v>
+      </c>
+      <c r="G227" s="24"/>
+      <c r="H227" s="22"/>
+    </row>
+    <row r="228" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A228" s="16">
+        <v>67</v>
+      </c>
+      <c r="B228" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C228" s="7" t="s">
+        <v>525</v>
+      </c>
+      <c r="D228" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E228" s="7" t="s">
         <v>412</v>
       </c>
-      <c r="F226" s="7" t="s">
+      <c r="F228" s="7" t="s">
         <v>411</v>
       </c>
-    </row>
-    <row r="227" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A227" s="16">
-        <v>67</v>
-      </c>
-      <c r="B227" s="7" t="s">
-        <v>123</v>
-      </c>
-      <c r="C227" s="7" t="s">
-        <v>525</v>
-      </c>
-      <c r="D227" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E227" s="7" t="s">
-        <v>414</v>
-      </c>
-      <c r="F227" s="7" t="s">
-        <v>406</v>
-      </c>
-    </row>
-    <row r="228" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A228" s="21">
-        <v>68</v>
-      </c>
-      <c r="B228" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="C228" s="23" t="s">
-        <v>525</v>
-      </c>
-      <c r="D228" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="E228" s="23" t="s">
-        <v>409</v>
-      </c>
-      <c r="F228" s="23" t="s">
-        <v>408</v>
-      </c>
-      <c r="G228" s="24"/>
-      <c r="H228" s="22"/>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A229" s="16">
+        <v>67</v>
+      </c>
+      <c r="B229" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C229" s="7" t="s">
+        <v>525</v>
+      </c>
+      <c r="D229" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E229" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="F229" s="7" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="230" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A230" s="21">
         <v>68</v>
       </c>
-      <c r="B229" s="7" t="s">
+      <c r="B230" s="23" t="s">
         <v>125</v>
       </c>
-      <c r="C229" s="7" t="s">
-        <v>525</v>
-      </c>
-      <c r="D229" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E229" s="7" t="s">
+      <c r="C230" s="23" t="s">
+        <v>525</v>
+      </c>
+      <c r="D230" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="E230" s="23" t="s">
+        <v>409</v>
+      </c>
+      <c r="F230" s="23" t="s">
+        <v>408</v>
+      </c>
+      <c r="G230" s="24"/>
+      <c r="H230" s="22"/>
+    </row>
+    <row r="231" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A231" s="16">
+        <v>68</v>
+      </c>
+      <c r="B231" s="7" t="s">
+        <v>125</v>
+      </c>
+      <c r="C231" s="7" t="s">
+        <v>525</v>
+      </c>
+      <c r="D231" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E231" s="7" t="s">
         <v>412</v>
       </c>
-      <c r="F229" s="7" t="s">
+      <c r="F231" s="7" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="230" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A230" s="16">
+    <row r="232" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A232" s="16">
         <v>68</v>
       </c>
-      <c r="B230" s="7" t="s">
+      <c r="B232" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="C230" s="7" t="s">
-        <v>525</v>
-      </c>
-      <c r="D230" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E230" s="7" t="s">
+      <c r="C232" s="7" t="s">
+        <v>525</v>
+      </c>
+      <c r="D232" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E232" s="7" t="s">
         <v>414</v>
       </c>
-      <c r="F230" s="7" t="s">
+      <c r="F232" s="7" t="s">
         <v>406</v>
       </c>
-    </row>
-    <row r="231" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A231" s="21">
-        <v>69</v>
-      </c>
-      <c r="B231" s="23" t="s">
-        <v>127</v>
-      </c>
-      <c r="C231" s="23" t="s">
-        <v>527</v>
-      </c>
-      <c r="D231" s="27"/>
-      <c r="E231" s="21"/>
-      <c r="F231" s="21"/>
-      <c r="G231" s="24"/>
-      <c r="H231" s="22"/>
-    </row>
-    <row r="232" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A232" s="21">
-        <v>70</v>
-      </c>
-      <c r="B232" s="23" t="s">
-        <v>149</v>
-      </c>
-      <c r="C232" s="23" t="s">
-        <v>527</v>
-      </c>
-      <c r="D232" s="27"/>
-      <c r="E232" s="21"/>
-      <c r="F232" s="21"/>
-      <c r="G232" s="24"/>
-      <c r="H232" s="22"/>
     </row>
     <row r="233" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A233" s="21">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="B233" s="23" t="s">
-        <v>153</v>
+        <v>127</v>
       </c>
       <c r="C233" s="23" t="s">
         <v>527</v>
@@ -22267,10 +22297,10 @@
     </row>
     <row r="234" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A234" s="21">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B234" s="23" t="s">
-        <v>155</v>
+        <v>149</v>
       </c>
       <c r="C234" s="23" t="s">
         <v>527</v>
@@ -22283,10 +22313,10 @@
     </row>
     <row r="235" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A235" s="21">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="B235" s="23" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="C235" s="23" t="s">
         <v>527</v>
@@ -22299,10 +22329,10 @@
     </row>
     <row r="236" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A236" s="21">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="B236" s="23" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="C236" s="23" t="s">
         <v>527</v>
@@ -22315,10 +22345,10 @@
     </row>
     <row r="237" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A237" s="21">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="B237" s="23" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="C237" s="23" t="s">
         <v>527</v>
@@ -22331,10 +22361,10 @@
     </row>
     <row r="238" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A238" s="21">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="B238" s="23" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C238" s="23" t="s">
         <v>527</v>
@@ -22347,10 +22377,10 @@
     </row>
     <row r="239" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A239" s="21">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="B239" s="23" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="C239" s="23" t="s">
         <v>527</v>
@@ -22363,10 +22393,10 @@
     </row>
     <row r="240" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A240" s="21">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="B240" s="23" t="s">
-        <v>129</v>
+        <v>163</v>
       </c>
       <c r="C240" s="23" t="s">
         <v>527</v>
@@ -22379,10 +22409,10 @@
     </row>
     <row r="241" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A241" s="21">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="B241" s="23" t="s">
-        <v>131</v>
+        <v>165</v>
       </c>
       <c r="C241" s="23" t="s">
         <v>527</v>
@@ -22395,10 +22425,10 @@
     </row>
     <row r="242" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A242" s="21">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="B242" s="23" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="C242" s="23" t="s">
         <v>527</v>
@@ -22411,10 +22441,10 @@
     </row>
     <row r="243" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A243" s="21">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="B243" s="23" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="C243" s="23" t="s">
         <v>527</v>
@@ -22427,10 +22457,10 @@
     </row>
     <row r="244" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A244" s="21">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="B244" s="23" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="C244" s="23" t="s">
         <v>527</v>
@@ -22443,10 +22473,10 @@
     </row>
     <row r="245" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A245" s="21">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B245" s="23" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="C245" s="23" t="s">
         <v>527</v>
@@ -22459,10 +22489,10 @@
     </row>
     <row r="246" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A246" s="21">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="B246" s="23" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="C246" s="23" t="s">
         <v>527</v>
@@ -22475,10 +22505,10 @@
     </row>
     <row r="247" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A247" s="21">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="B247" s="23" t="s">
-        <v>143</v>
+        <v>139</v>
       </c>
       <c r="C247" s="23" t="s">
         <v>527</v>
@@ -22491,10 +22521,10 @@
     </row>
     <row r="248" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A248" s="21">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="B248" s="23" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
       <c r="C248" s="23" t="s">
         <v>527</v>
@@ -22507,10 +22537,10 @@
     </row>
     <row r="249" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A249" s="21">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B249" s="23" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="C249" s="23" t="s">
         <v>527</v>
@@ -22523,10 +22553,10 @@
     </row>
     <row r="250" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A250" s="21">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="B250" s="23" t="s">
-        <v>151</v>
+        <v>145</v>
       </c>
       <c r="C250" s="23" t="s">
         <v>527</v>
@@ -22539,104 +22569,104 @@
     </row>
     <row r="251" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A251" s="21">
-        <v>89</v>
-      </c>
-      <c r="B251" s="21" t="s">
-        <v>167</v>
-      </c>
-      <c r="C251" s="21" t="s">
-        <v>525</v>
-      </c>
-      <c r="D251" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="E251" s="23" t="s">
-        <v>409</v>
-      </c>
-      <c r="F251" s="23" t="s">
-        <v>408</v>
-      </c>
+        <v>87</v>
+      </c>
+      <c r="B251" s="23" t="s">
+        <v>147</v>
+      </c>
+      <c r="C251" s="23" t="s">
+        <v>527</v>
+      </c>
+      <c r="D251" s="27"/>
+      <c r="E251" s="21"/>
+      <c r="F251" s="21"/>
       <c r="G251" s="24"/>
       <c r="H251" s="22"/>
     </row>
-    <row r="252" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A252" s="16">
+    <row r="252" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A252" s="21">
+        <v>88</v>
+      </c>
+      <c r="B252" s="23" t="s">
+        <v>151</v>
+      </c>
+      <c r="C252" s="23" t="s">
+        <v>527</v>
+      </c>
+      <c r="D252" s="27"/>
+      <c r="E252" s="21"/>
+      <c r="F252" s="21"/>
+      <c r="G252" s="24"/>
+      <c r="H252" s="22"/>
+    </row>
+    <row r="253" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A253" s="21">
         <v>89</v>
       </c>
-      <c r="B252" s="16" t="s">
+      <c r="B253" s="21" t="s">
         <v>167</v>
       </c>
-      <c r="C252" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D252" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E252" s="7" t="s">
+      <c r="C253" s="21" t="s">
+        <v>525</v>
+      </c>
+      <c r="D253" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="E253" s="23" t="s">
+        <v>409</v>
+      </c>
+      <c r="F253" s="23" t="s">
+        <v>408</v>
+      </c>
+      <c r="G253" s="24"/>
+      <c r="H253" s="22"/>
+    </row>
+    <row r="254" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A254" s="16">
+        <v>89</v>
+      </c>
+      <c r="B254" s="16" t="s">
+        <v>167</v>
+      </c>
+      <c r="C254" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D254" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E254" s="7" t="s">
         <v>412</v>
       </c>
-      <c r="F252" s="7" t="s">
+      <c r="F254" s="7" t="s">
         <v>411</v>
       </c>
     </row>
-    <row r="253" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A253" s="16">
+    <row r="255" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A255" s="16">
         <v>89</v>
       </c>
-      <c r="B253" s="16" t="s">
+      <c r="B255" s="16" t="s">
         <v>167</v>
       </c>
-      <c r="C253" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D253" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E253" s="7" t="s">
+      <c r="C255" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D255" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E255" s="7" t="s">
         <v>414</v>
       </c>
-      <c r="F253" s="7" t="s">
+      <c r="F255" s="7" t="s">
         <v>406</v>
       </c>
-    </row>
-    <row r="254" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A254" s="21">
-        <v>90</v>
-      </c>
-      <c r="B254" s="23" t="s">
-        <v>168</v>
-      </c>
-      <c r="C254" s="23" t="s">
-        <v>527</v>
-      </c>
-      <c r="D254" s="27"/>
-      <c r="E254" s="21"/>
-      <c r="F254" s="21"/>
-      <c r="G254" s="24"/>
-      <c r="H254" s="22"/>
-    </row>
-    <row r="255" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A255" s="21">
-        <v>91</v>
-      </c>
-      <c r="B255" s="23" t="s">
-        <v>169</v>
-      </c>
-      <c r="C255" s="23" t="s">
-        <v>527</v>
-      </c>
-      <c r="D255" s="27"/>
-      <c r="E255" s="21"/>
-      <c r="F255" s="21"/>
-      <c r="G255" s="24"/>
-      <c r="H255" s="22"/>
     </row>
     <row r="256" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A256" s="21">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="B256" s="23" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C256" s="23" t="s">
         <v>527</v>
@@ -22649,10 +22679,10 @@
     </row>
     <row r="257" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A257" s="21">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B257" s="23" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="C257" s="23" t="s">
         <v>527</v>
@@ -22665,10 +22695,10 @@
     </row>
     <row r="258" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A258" s="21">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="B258" s="23" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="C258" s="23" t="s">
         <v>527</v>
@@ -22681,13 +22711,13 @@
     </row>
     <row r="259" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A259" s="21">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="B259" s="23" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="C259" s="23" t="s">
-        <v>524</v>
+        <v>527</v>
       </c>
       <c r="D259" s="27"/>
       <c r="E259" s="21"/>
@@ -22697,65 +22727,57 @@
     </row>
     <row r="260" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A260" s="21">
-        <v>96</v>
-      </c>
-      <c r="B260" s="21" t="s">
-        <v>178</v>
-      </c>
-      <c r="C260" s="21" t="s">
-        <v>525</v>
-      </c>
-      <c r="D260" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="E260" s="23" t="s">
-        <v>409</v>
-      </c>
-      <c r="F260" s="23" t="s">
-        <v>403</v>
-      </c>
+        <v>94</v>
+      </c>
+      <c r="B260" s="23" t="s">
+        <v>174</v>
+      </c>
+      <c r="C260" s="23" t="s">
+        <v>527</v>
+      </c>
+      <c r="D260" s="27"/>
+      <c r="E260" s="21"/>
+      <c r="F260" s="21"/>
       <c r="G260" s="24"/>
       <c r="H260" s="22"/>
     </row>
-    <row r="261" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A261" s="16">
+    <row r="261" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A261" s="21">
+        <v>95</v>
+      </c>
+      <c r="B261" s="23" t="s">
+        <v>176</v>
+      </c>
+      <c r="C261" s="23" t="s">
+        <v>524</v>
+      </c>
+      <c r="D261" s="27"/>
+      <c r="E261" s="21"/>
+      <c r="F261" s="21"/>
+      <c r="G261" s="24"/>
+      <c r="H261" s="22"/>
+    </row>
+    <row r="262" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A262" s="21">
         <v>96</v>
       </c>
-      <c r="B261" s="16" t="s">
+      <c r="B262" s="21" t="s">
         <v>178</v>
       </c>
-      <c r="C261" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D261" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E261" s="7" t="s">
-        <v>469</v>
-      </c>
-      <c r="F261" s="7" t="s">
-        <v>476</v>
-      </c>
-    </row>
-    <row r="262" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A262" s="16">
-        <v>96</v>
-      </c>
-      <c r="B262" s="16" t="s">
-        <v>178</v>
-      </c>
-      <c r="C262" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D262" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E262" s="7" t="s">
-        <v>472</v>
-      </c>
-      <c r="F262" s="7" t="s">
-        <v>614</v>
-      </c>
+      <c r="C262" s="21" t="s">
+        <v>525</v>
+      </c>
+      <c r="D262" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="E262" s="23" t="s">
+        <v>409</v>
+      </c>
+      <c r="F262" s="23" t="s">
+        <v>403</v>
+      </c>
+      <c r="G262" s="24"/>
+      <c r="H262" s="22"/>
     </row>
     <row r="263" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A263" s="16">
@@ -22771,10 +22793,10 @@
         <v>0</v>
       </c>
       <c r="E263" s="7" t="s">
-        <v>449</v>
+        <v>469</v>
       </c>
       <c r="F263" s="7" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
     </row>
     <row r="264" spans="1:8" x14ac:dyDescent="0.25">
@@ -22791,10 +22813,10 @@
         <v>0</v>
       </c>
       <c r="E264" s="7" t="s">
-        <v>464</v>
+        <v>472</v>
       </c>
       <c r="F264" s="7" t="s">
-        <v>478</v>
+        <v>614</v>
       </c>
     </row>
     <row r="265" spans="1:8" x14ac:dyDescent="0.25">
@@ -22811,10 +22833,10 @@
         <v>0</v>
       </c>
       <c r="E265" s="7" t="s">
-        <v>412</v>
+        <v>449</v>
       </c>
       <c r="F265" s="7" t="s">
-        <v>479</v>
+        <v>477</v>
       </c>
     </row>
     <row r="266" spans="1:8" x14ac:dyDescent="0.25">
@@ -22831,105 +22853,105 @@
         <v>0</v>
       </c>
       <c r="E266" s="7" t="s">
+        <v>464</v>
+      </c>
+      <c r="F266" s="7" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="267" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A267" s="16">
+        <v>96</v>
+      </c>
+      <c r="B267" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="C267" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D267" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E267" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="F267" s="7" t="s">
+        <v>479</v>
+      </c>
+    </row>
+    <row r="268" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A268" s="16">
+        <v>96</v>
+      </c>
+      <c r="B268" s="16" t="s">
+        <v>178</v>
+      </c>
+      <c r="C268" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D268" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E268" s="7" t="s">
         <v>414</v>
       </c>
-      <c r="F266" s="7" t="s">
+      <c r="F268" s="7" t="s">
         <v>406</v>
       </c>
-    </row>
-    <row r="267" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A267" s="21">
-        <v>97</v>
-      </c>
-      <c r="B267" s="21" t="s">
-        <v>180</v>
-      </c>
-      <c r="C267" s="21" t="s">
-        <v>527</v>
-      </c>
-      <c r="D267" s="27"/>
-      <c r="E267" s="21"/>
-      <c r="F267" s="21"/>
-      <c r="G267" s="24"/>
-      <c r="H267" s="22"/>
-    </row>
-    <row r="268" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A268" s="21">
-        <v>98</v>
-      </c>
-      <c r="B268" s="21" t="s">
-        <v>182</v>
-      </c>
-      <c r="C268" s="21" t="s">
-        <v>527</v>
-      </c>
-      <c r="D268" s="27"/>
-      <c r="E268" s="21"/>
-      <c r="F268" s="21"/>
-      <c r="G268" s="24"/>
-      <c r="H268" s="22"/>
     </row>
     <row r="269" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A269" s="21">
-        <v>99</v>
-      </c>
-      <c r="B269" s="23" t="s">
-        <v>183</v>
-      </c>
-      <c r="C269" s="23" t="s">
-        <v>525</v>
-      </c>
-      <c r="D269" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="E269" s="23" t="s">
-        <v>469</v>
-      </c>
-      <c r="F269" s="23" t="s">
-        <v>615</v>
-      </c>
+        <v>97</v>
+      </c>
+      <c r="B269" s="21" t="s">
+        <v>180</v>
+      </c>
+      <c r="C269" s="21" t="s">
+        <v>527</v>
+      </c>
+      <c r="D269" s="27"/>
+      <c r="E269" s="21"/>
+      <c r="F269" s="21"/>
       <c r="G269" s="24"/>
       <c r="H269" s="22"/>
     </row>
-    <row r="270" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A270" s="16">
+    <row r="270" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A270" s="21">
+        <v>98</v>
+      </c>
+      <c r="B270" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="C270" s="21" t="s">
+        <v>527</v>
+      </c>
+      <c r="D270" s="27"/>
+      <c r="E270" s="21"/>
+      <c r="F270" s="21"/>
+      <c r="G270" s="24"/>
+      <c r="H270" s="22"/>
+    </row>
+    <row r="271" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A271" s="21">
         <v>99</v>
       </c>
-      <c r="B270" s="7" t="s">
+      <c r="B271" s="23" t="s">
         <v>183</v>
       </c>
-      <c r="C270" s="7" t="s">
-        <v>525</v>
-      </c>
-      <c r="D270" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E270" s="7" t="s">
-        <v>521</v>
-      </c>
-      <c r="F270" s="7" t="s">
-        <v>616</v>
-      </c>
-    </row>
-    <row r="271" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A271" s="16">
-        <v>99</v>
-      </c>
-      <c r="B271" s="7" t="s">
-        <v>183</v>
-      </c>
-      <c r="C271" s="7" t="s">
-        <v>525</v>
-      </c>
-      <c r="D271" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E271" s="7" t="s">
-        <v>414</v>
-      </c>
-      <c r="F271" s="7" t="s">
-        <v>465</v>
-      </c>
+      <c r="C271" s="23" t="s">
+        <v>525</v>
+      </c>
+      <c r="D271" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="E271" s="23" t="s">
+        <v>469</v>
+      </c>
+      <c r="F271" s="23" t="s">
+        <v>615</v>
+      </c>
+      <c r="G271" s="24"/>
+      <c r="H271" s="22"/>
     </row>
     <row r="272" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A272" s="16">
@@ -22945,53 +22967,61 @@
         <v>0</v>
       </c>
       <c r="E272" s="7" t="s">
+        <v>521</v>
+      </c>
+      <c r="F272" s="7" t="s">
+        <v>616</v>
+      </c>
+    </row>
+    <row r="273" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A273" s="16">
+        <v>99</v>
+      </c>
+      <c r="B273" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C273" s="7" t="s">
+        <v>525</v>
+      </c>
+      <c r="D273" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E273" s="7" t="s">
+        <v>414</v>
+      </c>
+      <c r="F273" s="7" t="s">
+        <v>465</v>
+      </c>
+    </row>
+    <row r="274" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A274" s="16">
+        <v>99</v>
+      </c>
+      <c r="B274" s="7" t="s">
+        <v>183</v>
+      </c>
+      <c r="C274" s="7" t="s">
+        <v>525</v>
+      </c>
+      <c r="D274" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E274" s="7" t="s">
         <v>514</v>
       </c>
-      <c r="F272" s="7" t="s">
+      <c r="F274" s="7" t="s">
         <v>441</v>
       </c>
-      <c r="H272" t="s">
+      <c r="H274" t="s">
         <v>569</v>
       </c>
-    </row>
-    <row r="273" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A273" s="21">
-        <v>100</v>
-      </c>
-      <c r="B273" s="23" t="s">
-        <v>532</v>
-      </c>
-      <c r="C273" s="23" t="s">
-        <v>527</v>
-      </c>
-      <c r="D273" s="27"/>
-      <c r="E273" s="21"/>
-      <c r="F273" s="21"/>
-      <c r="G273" s="24"/>
-      <c r="H273" s="22"/>
-    </row>
-    <row r="274" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A274" s="21">
-        <v>101</v>
-      </c>
-      <c r="B274" s="23" t="s">
-        <v>533</v>
-      </c>
-      <c r="C274" s="23" t="s">
-        <v>527</v>
-      </c>
-      <c r="D274" s="27"/>
-      <c r="E274" s="21"/>
-      <c r="F274" s="21"/>
-      <c r="G274" s="24"/>
-      <c r="H274" s="22"/>
     </row>
     <row r="275" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A275" s="21">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="B275" s="23" t="s">
-        <v>185</v>
+        <v>532</v>
       </c>
       <c r="C275" s="23" t="s">
         <v>527</v>
@@ -23004,13 +23034,13 @@
     </row>
     <row r="276" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A276" s="21">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="B276" s="23" t="s">
-        <v>186</v>
+        <v>533</v>
       </c>
       <c r="C276" s="23" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="D276" s="27"/>
       <c r="E276" s="21"/>
@@ -23020,13 +23050,13 @@
     </row>
     <row r="277" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A277" s="21">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B277" s="23" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="C277" s="23" t="s">
-        <v>534</v>
+        <v>527</v>
       </c>
       <c r="D277" s="27"/>
       <c r="E277" s="21"/>
@@ -23036,65 +23066,57 @@
     </row>
     <row r="278" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A278" s="21">
-        <v>105</v>
-      </c>
-      <c r="B278" s="21" t="s">
-        <v>197</v>
-      </c>
-      <c r="C278" s="21" t="s">
-        <v>525</v>
-      </c>
-      <c r="D278" s="27" t="b">
-        <v>0</v>
-      </c>
-      <c r="E278" s="23" t="s">
-        <v>409</v>
-      </c>
-      <c r="F278" s="23" t="s">
-        <v>408</v>
-      </c>
+        <v>103</v>
+      </c>
+      <c r="B278" s="23" t="s">
+        <v>186</v>
+      </c>
+      <c r="C278" s="23" t="s">
+        <v>534</v>
+      </c>
+      <c r="D278" s="27"/>
+      <c r="E278" s="21"/>
+      <c r="F278" s="21"/>
       <c r="G278" s="24"/>
       <c r="H278" s="22"/>
     </row>
-    <row r="279" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A279" s="16">
+    <row r="279" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A279" s="21">
+        <v>104</v>
+      </c>
+      <c r="B279" s="23" t="s">
+        <v>191</v>
+      </c>
+      <c r="C279" s="23" t="s">
+        <v>534</v>
+      </c>
+      <c r="D279" s="27"/>
+      <c r="E279" s="21"/>
+      <c r="F279" s="21"/>
+      <c r="G279" s="24"/>
+      <c r="H279" s="22"/>
+    </row>
+    <row r="280" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A280" s="21">
         <v>105</v>
       </c>
-      <c r="B279" s="16" t="s">
+      <c r="B280" s="21" t="s">
         <v>197</v>
       </c>
-      <c r="C279" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D279" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E279" s="7" t="s">
-        <v>412</v>
-      </c>
-      <c r="F279" s="7" t="s">
-        <v>411</v>
-      </c>
-    </row>
-    <row r="280" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A280" s="16">
-        <v>105</v>
-      </c>
-      <c r="B280" s="16" t="s">
-        <v>197</v>
-      </c>
-      <c r="C280" s="16" t="s">
-        <v>525</v>
-      </c>
-      <c r="D280" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="E280" s="7" t="s">
-        <v>467</v>
-      </c>
-      <c r="F280" s="7" t="s">
-        <v>480</v>
-      </c>
+      <c r="C280" s="21" t="s">
+        <v>525</v>
+      </c>
+      <c r="D280" s="27" t="b">
+        <v>0</v>
+      </c>
+      <c r="E280" s="23" t="s">
+        <v>409</v>
+      </c>
+      <c r="F280" s="23" t="s">
+        <v>408</v>
+      </c>
+      <c r="G280" s="24"/>
+      <c r="H280" s="22"/>
     </row>
     <row r="281" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A281" s="16">
@@ -23110,45 +23132,86 @@
         <v>0</v>
       </c>
       <c r="E281" s="7" t="s">
+        <v>412</v>
+      </c>
+      <c r="F281" s="7" t="s">
+        <v>411</v>
+      </c>
+    </row>
+    <row r="282" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A282" s="16">
+        <v>105</v>
+      </c>
+      <c r="B282" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="C282" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D282" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E282" s="7" t="s">
+        <v>467</v>
+      </c>
+      <c r="F282" s="7" t="s">
+        <v>480</v>
+      </c>
+    </row>
+    <row r="283" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="A283" s="16">
+        <v>105</v>
+      </c>
+      <c r="B283" s="16" t="s">
+        <v>197</v>
+      </c>
+      <c r="C283" s="16" t="s">
+        <v>525</v>
+      </c>
+      <c r="D283" s="28" t="b">
+        <v>0</v>
+      </c>
+      <c r="E283" s="7" t="s">
         <v>414</v>
       </c>
-      <c r="F281" s="7" t="s">
+      <c r="F283" s="7" t="s">
         <v>406</v>
       </c>
     </row>
-    <row r="282" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A282" s="21">
+    <row r="284" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A284" s="21">
         <v>106</v>
       </c>
-      <c r="B282" s="23" t="s">
+      <c r="B284" s="23" t="s">
         <v>199</v>
       </c>
-      <c r="C282" s="23" t="s">
+      <c r="C284" s="23" t="s">
         <v>527</v>
       </c>
-      <c r="D282" s="27"/>
-      <c r="E282" s="21"/>
-      <c r="F282" s="21"/>
-      <c r="G282" s="24"/>
-      <c r="H282" s="22"/>
-    </row>
-    <row r="283" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A283" s="21">
+      <c r="D284" s="27"/>
+      <c r="E284" s="21"/>
+      <c r="F284" s="21"/>
+      <c r="G284" s="24"/>
+      <c r="H284" s="22"/>
+    </row>
+    <row r="285" spans="1:8" s="25" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A285" s="21">
         <v>107</v>
       </c>
-      <c r="B283" s="23" t="s">
+      <c r="B285" s="23" t="s">
         <v>535</v>
       </c>
-      <c r="C283" s="23" t="s">
+      <c r="C285" s="23" t="s">
         <v>527</v>
       </c>
-      <c r="D283" s="27"/>
-      <c r="E283" s="21"/>
-      <c r="F283" s="21"/>
-      <c r="G283" s="24"/>
-      <c r="H283" s="22"/>
+      <c r="D285" s="27"/>
+      <c r="E285" s="21"/>
+      <c r="F285" s="21"/>
+      <c r="G285" s="24"/>
+      <c r="H285" s="22"/>
     </row>
   </sheetData>
+  <autoFilter ref="A1:H285" xr:uid="{51D60DD1-DC0B-4658-A996-7DC0B41964ED}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -24071,6 +24134,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{94E354B3-65EF-432B-8711-1350D70DF596}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:G219"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -24106,7 +24170,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -24123,7 +24187,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>6</v>
       </c>
@@ -24140,7 +24204,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>6</v>
       </c>
@@ -24157,7 +24221,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -24174,7 +24238,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>6</v>
       </c>
@@ -24191,7 +24255,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>6</v>
       </c>
@@ -24208,7 +24272,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -24225,7 +24289,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>9</v>
       </c>
@@ -24242,7 +24306,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>9</v>
       </c>
@@ -24259,7 +24323,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>10</v>
       </c>
@@ -24276,7 +24340,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>10</v>
       </c>
@@ -24293,7 +24357,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>10</v>
       </c>
@@ -24463,7 +24527,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>22</v>
       </c>
@@ -24480,7 +24544,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>22</v>
       </c>
@@ -24497,7 +24561,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>22</v>
       </c>
@@ -24514,7 +24578,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>22</v>
       </c>
@@ -24531,7 +24595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>22</v>
       </c>
@@ -24548,7 +24612,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>22</v>
       </c>
@@ -24565,7 +24629,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>22</v>
       </c>
@@ -24582,7 +24646,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>40</v>
       </c>
@@ -24599,7 +24663,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>40</v>
       </c>
@@ -24616,7 +24680,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>40</v>
       </c>
@@ -24633,7 +24697,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>40</v>
       </c>
@@ -24650,7 +24714,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>40</v>
       </c>
@@ -24667,7 +24731,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>40</v>
       </c>
@@ -24684,7 +24748,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>40</v>
       </c>
@@ -24701,7 +24765,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>40</v>
       </c>
@@ -24718,7 +24782,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>44</v>
       </c>
@@ -24738,7 +24802,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>44</v>
       </c>
@@ -24758,7 +24822,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>44</v>
       </c>
@@ -24778,7 +24842,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>44</v>
       </c>
@@ -24798,7 +24862,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>44</v>
       </c>
@@ -24818,7 +24882,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>44</v>
       </c>
@@ -24838,7 +24902,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>44</v>
       </c>
@@ -24858,7 +24922,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>44</v>
       </c>
@@ -24878,7 +24942,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>44</v>
       </c>
@@ -24898,7 +24962,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>46</v>
       </c>
@@ -24918,7 +24982,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>46</v>
       </c>
@@ -24938,7 +25002,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>46</v>
       </c>
@@ -24958,7 +25022,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>46</v>
       </c>
@@ -24978,7 +25042,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>46</v>
       </c>
@@ -24998,7 +25062,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>46</v>
       </c>
@@ -25018,7 +25082,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>46</v>
       </c>
@@ -25038,7 +25102,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>46</v>
       </c>
@@ -25058,7 +25122,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>46</v>
       </c>
@@ -25078,7 +25142,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>46</v>
       </c>
@@ -25098,7 +25162,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>48</v>
       </c>
@@ -25115,7 +25179,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>48</v>
       </c>
@@ -25132,7 +25196,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>48</v>
       </c>
@@ -25149,7 +25213,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>50</v>
       </c>
@@ -25166,7 +25230,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>50</v>
       </c>
@@ -25183,7 +25247,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>50</v>
       </c>
@@ -25200,7 +25264,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>52</v>
       </c>
@@ -25217,7 +25281,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:6" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>52</v>
       </c>
@@ -25234,7 +25298,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>52</v>
       </c>
@@ -25251,7 +25315,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>52</v>
       </c>
@@ -25268,7 +25332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>52</v>
       </c>
@@ -25285,7 +25349,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>52</v>
       </c>
@@ -25302,7 +25366,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>52</v>
       </c>
@@ -25319,7 +25383,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>54</v>
       </c>
@@ -25336,7 +25400,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>54</v>
       </c>
@@ -25353,7 +25417,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>54</v>
       </c>
@@ -25370,7 +25434,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>56</v>
       </c>
@@ -25387,7 +25451,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>56</v>
       </c>
@@ -25404,7 +25468,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>56</v>
       </c>
@@ -25421,7 +25485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>58</v>
       </c>
@@ -25438,7 +25502,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>58</v>
       </c>
@@ -25455,7 +25519,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>58</v>
       </c>
@@ -25472,7 +25536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>64</v>
       </c>
@@ -25489,7 +25553,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>64</v>
       </c>
@@ -25506,7 +25570,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>64</v>
       </c>
@@ -25523,7 +25587,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>64</v>
       </c>
@@ -25540,7 +25604,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>64</v>
       </c>
@@ -25557,7 +25621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>64</v>
       </c>
@@ -25574,7 +25638,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>64</v>
       </c>
@@ -25591,7 +25655,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>64</v>
       </c>
@@ -25608,7 +25672,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>64</v>
       </c>
@@ -25625,7 +25689,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>64</v>
       </c>
@@ -25642,7 +25706,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>66</v>
       </c>
@@ -25659,7 +25723,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" t="s">
         <v>66</v>
       </c>
@@ -25676,7 +25740,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" t="s">
         <v>66</v>
       </c>
@@ -25693,7 +25757,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" t="s">
         <v>83</v>
       </c>
@@ -25710,7 +25774,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" t="s">
         <v>83</v>
       </c>
@@ -25727,7 +25791,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" t="s">
         <v>83</v>
       </c>
@@ -25744,7 +25808,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" t="s">
         <v>83</v>
       </c>
@@ -25761,7 +25825,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" t="s">
         <v>83</v>
       </c>
@@ -25778,7 +25842,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" t="s">
         <v>83</v>
       </c>
@@ -25795,7 +25859,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" t="s">
         <v>83</v>
       </c>
@@ -25815,7 +25879,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" t="s">
         <v>85</v>
       </c>
@@ -25832,7 +25896,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" t="s">
         <v>85</v>
       </c>
@@ -25849,7 +25913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" t="s">
         <v>85</v>
       </c>
@@ -25866,7 +25930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" t="s">
         <v>85</v>
       </c>
@@ -25883,7 +25947,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" t="s">
         <v>85</v>
       </c>
@@ -25900,7 +25964,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" t="s">
         <v>85</v>
       </c>
@@ -25917,7 +25981,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" t="s">
         <v>85</v>
       </c>
@@ -25934,7 +25998,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" t="s">
         <v>87</v>
       </c>
@@ -25951,7 +26015,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" t="s">
         <v>87</v>
       </c>
@@ -25968,7 +26032,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" t="s">
         <v>87</v>
       </c>
@@ -25985,7 +26049,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" t="s">
         <v>91</v>
       </c>
@@ -26002,7 +26066,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" t="s">
         <v>91</v>
       </c>
@@ -26019,7 +26083,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" t="s">
         <v>91</v>
       </c>
@@ -26036,7 +26100,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" t="s">
         <v>91</v>
       </c>
@@ -26053,7 +26117,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" t="s">
         <v>91</v>
       </c>
@@ -26070,7 +26134,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" t="s">
         <v>91</v>
       </c>
@@ -26087,7 +26151,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" t="s">
         <v>91</v>
       </c>
@@ -26104,7 +26168,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" t="s">
         <v>91</v>
       </c>
@@ -26121,7 +26185,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" t="s">
         <v>91</v>
       </c>
@@ -26138,7 +26202,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" t="s">
         <v>91</v>
       </c>
@@ -26155,7 +26219,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" t="s">
         <v>93</v>
       </c>
@@ -26172,7 +26236,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" t="s">
         <v>93</v>
       </c>
@@ -26189,7 +26253,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" t="s">
         <v>93</v>
       </c>
@@ -26206,7 +26270,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="122" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" t="s">
         <v>93</v>
       </c>
@@ -26223,7 +26287,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="123" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" t="s">
         <v>93</v>
       </c>
@@ -26240,7 +26304,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" t="s">
         <v>93</v>
       </c>
@@ -26257,7 +26321,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" t="s">
         <v>95</v>
       </c>
@@ -26274,7 +26338,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="126" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" t="s">
         <v>95</v>
       </c>
@@ -26291,7 +26355,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="127" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" t="s">
         <v>95</v>
       </c>
@@ -26308,7 +26372,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" t="s">
         <v>97</v>
       </c>
@@ -26325,7 +26389,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="129" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" t="s">
         <v>97</v>
       </c>
@@ -26342,7 +26406,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="130" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" t="s">
         <v>97</v>
       </c>
@@ -26359,7 +26423,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="131" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" t="s">
         <v>99</v>
       </c>
@@ -26376,7 +26440,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="132" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" t="s">
         <v>99</v>
       </c>
@@ -26393,7 +26457,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="133" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" t="s">
         <v>99</v>
       </c>
@@ -26410,7 +26474,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="134" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" t="s">
         <v>101</v>
       </c>
@@ -26427,7 +26491,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="135" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" t="s">
         <v>101</v>
       </c>
@@ -26444,7 +26508,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="136" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" t="s">
         <v>101</v>
       </c>
@@ -26461,7 +26525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="137" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" t="s">
         <v>103</v>
       </c>
@@ -26478,7 +26542,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="138" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" t="s">
         <v>103</v>
       </c>
@@ -26495,7 +26559,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="139" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" t="s">
         <v>103</v>
       </c>
@@ -26512,7 +26576,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="140" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" t="s">
         <v>105</v>
       </c>
@@ -26529,7 +26593,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="141" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" t="s">
         <v>105</v>
       </c>
@@ -26546,7 +26610,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="142" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" t="s">
         <v>105</v>
       </c>
@@ -26563,7 +26627,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="143" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" t="s">
         <v>107</v>
       </c>
@@ -26580,7 +26644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="144" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" t="s">
         <v>107</v>
       </c>
@@ -26597,7 +26661,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="145" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" t="s">
         <v>107</v>
       </c>
@@ -26614,7 +26678,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="146" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" t="s">
         <v>109</v>
       </c>
@@ -26631,7 +26695,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="147" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" t="s">
         <v>109</v>
       </c>
@@ -26648,7 +26712,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="148" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" t="s">
         <v>109</v>
       </c>
@@ -26665,7 +26729,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="149" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" t="s">
         <v>111</v>
       </c>
@@ -26682,7 +26746,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="150" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" t="s">
         <v>111</v>
       </c>
@@ -26699,7 +26763,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="151" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" t="s">
         <v>111</v>
       </c>
@@ -26716,7 +26780,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="152" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" t="s">
         <v>113</v>
       </c>
@@ -26733,7 +26797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="153" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" t="s">
         <v>113</v>
       </c>
@@ -26750,7 +26814,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="154" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" t="s">
         <v>113</v>
       </c>
@@ -26767,7 +26831,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="155" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" t="s">
         <v>115</v>
       </c>
@@ -26784,7 +26848,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="156" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" t="s">
         <v>115</v>
       </c>
@@ -26801,7 +26865,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="157" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" t="s">
         <v>115</v>
       </c>
@@ -26818,7 +26882,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="158" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" t="s">
         <v>117</v>
       </c>
@@ -26835,7 +26899,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="159" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" t="s">
         <v>117</v>
       </c>
@@ -26852,7 +26916,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="160" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" t="s">
         <v>117</v>
       </c>
@@ -26869,7 +26933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="161" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" t="s">
         <v>119</v>
       </c>
@@ -26886,7 +26950,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="162" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" t="s">
         <v>119</v>
       </c>
@@ -26903,7 +26967,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="163" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" t="s">
         <v>119</v>
       </c>
@@ -26920,7 +26984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="164" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" t="s">
         <v>121</v>
       </c>
@@ -26937,7 +27001,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="165" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" t="s">
         <v>121</v>
       </c>
@@ -26954,7 +27018,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="166" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" t="s">
         <v>121</v>
       </c>
@@ -26971,7 +27035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="167" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" t="s">
         <v>121</v>
       </c>
@@ -26988,7 +27052,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="168" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" t="s">
         <v>121</v>
       </c>
@@ -27005,7 +27069,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="169" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" t="s">
         <v>121</v>
       </c>
@@ -27022,7 +27086,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="170" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" t="s">
         <v>121</v>
       </c>
@@ -27039,7 +27103,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="171" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" t="s">
         <v>121</v>
       </c>
@@ -27056,7 +27120,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="172" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" t="s">
         <v>121</v>
       </c>
@@ -27073,7 +27137,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="173" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" t="s">
         <v>121</v>
       </c>
@@ -27090,7 +27154,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="174" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" t="s">
         <v>121</v>
       </c>
@@ -27107,7 +27171,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="175" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" t="s">
         <v>121</v>
       </c>
@@ -27124,7 +27188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="176" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" t="s">
         <v>121</v>
       </c>
@@ -27141,7 +27205,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="177" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" t="s">
         <v>121</v>
       </c>
@@ -27158,7 +27222,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="178" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" t="s">
         <v>121</v>
       </c>
@@ -27175,7 +27239,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="179" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" t="s">
         <v>121</v>
       </c>
@@ -27192,7 +27256,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="180" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" t="s">
         <v>121</v>
       </c>
@@ -27209,7 +27273,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="181" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" t="s">
         <v>121</v>
       </c>
@@ -27226,7 +27290,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="182" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" t="s">
         <v>121</v>
       </c>
@@ -27243,7 +27307,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="183" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" t="s">
         <v>121</v>
       </c>
@@ -27260,7 +27324,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="184" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" t="s">
         <v>121</v>
       </c>
@@ -27277,7 +27341,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="185" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" t="s">
         <v>121</v>
       </c>
@@ -27294,7 +27358,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="186" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" t="s">
         <v>121</v>
       </c>
@@ -27311,7 +27375,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="187" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" t="s">
         <v>121</v>
       </c>
@@ -27328,7 +27392,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="188" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" t="s">
         <v>121</v>
       </c>
@@ -27345,7 +27409,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="189" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" t="s">
         <v>121</v>
       </c>
@@ -27362,7 +27426,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="190" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" t="s">
         <v>121</v>
       </c>
@@ -27379,7 +27443,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="191" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" t="s">
         <v>121</v>
       </c>
@@ -27396,7 +27460,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="192" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" t="s">
         <v>121</v>
       </c>
@@ -27413,7 +27477,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="193" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" t="s">
         <v>121</v>
       </c>
@@ -27430,7 +27494,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="194" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" t="s">
         <v>121</v>
       </c>
@@ -27447,7 +27511,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="195" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" t="s">
         <v>121</v>
       </c>
@@ -27464,7 +27528,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="196" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" t="s">
         <v>123</v>
       </c>
@@ -27481,7 +27545,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="197" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" t="s">
         <v>123</v>
       </c>
@@ -27498,7 +27562,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="198" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" t="s">
         <v>123</v>
       </c>
@@ -27515,7 +27579,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="199" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" t="s">
         <v>125</v>
       </c>
@@ -27532,7 +27596,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="200" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" t="s">
         <v>125</v>
       </c>
@@ -27549,7 +27613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="201" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" t="s">
         <v>125</v>
       </c>
@@ -27566,7 +27630,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="202" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" t="s">
         <v>167</v>
       </c>
@@ -27583,7 +27647,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="203" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" t="s">
         <v>167</v>
       </c>
@@ -27600,7 +27664,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="204" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" t="s">
         <v>167</v>
       </c>
@@ -27617,7 +27681,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="205" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" t="s">
         <v>178</v>
       </c>
@@ -27634,7 +27698,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="206" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" t="s">
         <v>178</v>
       </c>
@@ -27651,7 +27715,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="207" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" t="s">
         <v>178</v>
       </c>
@@ -27668,7 +27732,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="208" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" t="s">
         <v>178</v>
       </c>
@@ -27685,7 +27749,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="209" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" t="s">
         <v>178</v>
       </c>
@@ -27702,7 +27766,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="210" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" t="s">
         <v>178</v>
       </c>
@@ -27719,7 +27783,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="211" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" t="s">
         <v>178</v>
       </c>
@@ -27736,7 +27800,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="212" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" t="s">
         <v>183</v>
       </c>
@@ -27753,7 +27817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="213" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" t="s">
         <v>183</v>
       </c>
@@ -27770,7 +27834,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="214" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" t="s">
         <v>183</v>
       </c>
@@ -27787,7 +27851,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="215" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" t="s">
         <v>183</v>
       </c>
@@ -27807,7 +27871,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="216" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" t="s">
         <v>197</v>
       </c>
@@ -27824,7 +27888,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="217" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" t="s">
         <v>197</v>
       </c>
@@ -27841,7 +27905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="218" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" t="s">
         <v>197</v>
       </c>
@@ -27858,7 +27922,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="219" spans="1:7" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" t="s">
         <v>197</v>
       </c>
@@ -27876,6 +27940,13 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:G219" xr:uid="{94E354B3-65EF-432B-8711-1350D70DF596}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="certifier_designation"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Resources/Crosswalks and Schemas.xlsx
+++ b/Resources/Crosswalks and Schemas.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{684BAA3E-912E-4C3C-9331-4EBD82BCC5EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8280" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8280" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="3" r:id="rId1"/>

--- a/Resources/Crosswalks and Schemas.xlsx
+++ b/Resources/Crosswalks and Schemas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SHDTJB\Documents\LocalSave\Code\R\GitHub\WA-DOH-CHS-Death-Files-ETL\Resources\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{684BAA3E-912E-4C3C-9331-4EBD82BCC5EB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9D39953-78CA-41FC-A735-246E5F0FE2BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="8280" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8280" yWindow="-16320" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="README" sheetId="3" r:id="rId1"/>
@@ -2294,97 +2294,6 @@
   </si>
   <si>
     <t>harmonized_data_schema</t>
-  </si>
-  <si>
-    <r>
-      <t>1. Open the new annual data vintage to identify if any categorical variable values need to be recoded. Specifically, this would be instances where categorical/factor variable values do not align with provided factor values in the harmonized_data_schema sheet. 
-2. (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>If recoding needed</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">) Add rows to the bottom of the excel sheet with </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>file_year</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> = YYYY (to the specific year of the data vintage)
-3. (</t>
-    </r>
-    <r>
-      <rPr>
-        <i/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>If recoding needed</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve">) Mark </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>review_flag</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> = TRUE if any categorical variable value recodings need to be discussed with WA DOH SMEs. Run Scripts/dq_review.R to get a summary of all missing and flagged values.</t>
-    </r>
   </si>
   <si>
     <r>
@@ -2681,6 +2590,97 @@
       <t>) Add 1 row per factor level/label. (Example: armed_forces has 3 factor levels, and received 3 factors)</t>
     </r>
   </si>
+  <si>
+    <r>
+      <t>1. Open the new annual data vintage to identify if any categorical variable values need to be recoded. Specifically, this would be instances where categorical/factor variable values do not align with provided factor values in the harmonized_data_schema sheet. 
+2. (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>If recoding needed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">) Add rows to the bottom of the excel sheet with </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>file_year</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = YYYY (to the specific year of the data vintage)
+3. (</t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>If recoding needed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">) Mark </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>review_flag</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> = TRUE if any categorical variable value recodings need to be discussed with WA DOH SMEs. Run Scripts/crosswalk_review.R to get a summary of all missing and flagged values.</t>
+    </r>
+  </si>
 </sst>
 </file>
 
@@ -2785,7 +2785,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -2859,22 +2859,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2904,31 +2888,6 @@
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="22">
-    <dxf>
-      <font>
-        <b/>
-        <i val="0"/>
-        <strike val="0"/>
-        <condense val="0"/>
-        <extend val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor indexed="64"/>
-          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
-        </patternFill>
-      </fill>
-      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -2992,6 +2951,31 @@
     <dxf>
       <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor indexed="64"/>
+          <bgColor theme="0" tint="-4.9989318521683403E-2"/>
+        </patternFill>
+      </fill>
+      <alignment horizontal="center" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
@@ -3006,25 +2990,25 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2B988634-0A3F-4218-A737-C86216687859}" name="Table1" displayName="Table1" ref="A1:P106" totalsRowShown="0" headerRowDxfId="0" dataDxfId="21">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2B988634-0A3F-4218-A737-C86216687859}" name="Table1" displayName="Table1" ref="A1:P106" totalsRowShown="0" headerRowDxfId="21" dataDxfId="20">
   <autoFilter ref="A1:P106" xr:uid="{2B988634-0A3F-4218-A737-C86216687859}"/>
   <tableColumns count="16">
     <tableColumn id="1" xr3:uid="{62641E4A-1712-44E6-AD94-98AC729FB684}" name="to_name"/>
-    <tableColumn id="3" xr3:uid="{C41F7DDD-17A6-4681-B283-B0A121BCE584}" name="2010" dataDxfId="20"/>
-    <tableColumn id="4" xr3:uid="{366E8C38-CEEF-443A-AC7D-6E4CCC878386}" name="2011" dataDxfId="19"/>
-    <tableColumn id="5" xr3:uid="{2EC711C4-D300-4A9A-9B5D-EBA505809A16}" name="2012" dataDxfId="18"/>
-    <tableColumn id="6" xr3:uid="{0831D495-FA20-4737-AAA6-29444344B6C3}" name="2013" dataDxfId="17"/>
-    <tableColumn id="7" xr3:uid="{8825A97F-2EA3-4A37-A175-2F112365AAD2}" name="2014" dataDxfId="16"/>
-    <tableColumn id="8" xr3:uid="{176F4B23-1C40-46DA-BE31-52E33E59861E}" name="2015" dataDxfId="15"/>
-    <tableColumn id="9" xr3:uid="{3B1A8B4A-CD19-420A-8B55-D1E6E71036BF}" name="2016" dataDxfId="14"/>
-    <tableColumn id="10" xr3:uid="{8A13625C-A654-46AC-A558-DE0A972F322D}" name="2017" dataDxfId="13"/>
-    <tableColumn id="11" xr3:uid="{99E5B31D-42FA-47A4-B981-3A500BCD39D5}" name="2018" dataDxfId="12"/>
-    <tableColumn id="12" xr3:uid="{41FACBA7-3939-45A7-AB50-B7A958216469}" name="2019" dataDxfId="11"/>
-    <tableColumn id="13" xr3:uid="{1949E823-8768-46FD-8E24-872E7A0FC375}" name="2020" dataDxfId="10"/>
-    <tableColumn id="14" xr3:uid="{8E404941-341D-4DB3-A956-B66D4D2E8126}" name="2021" dataDxfId="9"/>
-    <tableColumn id="15" xr3:uid="{704B145E-914A-41F3-A348-5BCF98CDA78F}" name="2022" dataDxfId="8"/>
-    <tableColumn id="16" xr3:uid="{CFB54067-4688-4253-A746-1C1D1912493F}" name="2023" dataDxfId="7"/>
-    <tableColumn id="17" xr3:uid="{F286FA37-E091-4F76-9852-EC5DACED56CD}" name="2024" dataDxfId="6"/>
+    <tableColumn id="3" xr3:uid="{C41F7DDD-17A6-4681-B283-B0A121BCE584}" name="2010" dataDxfId="19"/>
+    <tableColumn id="4" xr3:uid="{366E8C38-CEEF-443A-AC7D-6E4CCC878386}" name="2011" dataDxfId="18"/>
+    <tableColumn id="5" xr3:uid="{2EC711C4-D300-4A9A-9B5D-EBA505809A16}" name="2012" dataDxfId="17"/>
+    <tableColumn id="6" xr3:uid="{0831D495-FA20-4737-AAA6-29444344B6C3}" name="2013" dataDxfId="16"/>
+    <tableColumn id="7" xr3:uid="{8825A97F-2EA3-4A37-A175-2F112365AAD2}" name="2014" dataDxfId="15"/>
+    <tableColumn id="8" xr3:uid="{176F4B23-1C40-46DA-BE31-52E33E59861E}" name="2015" dataDxfId="14"/>
+    <tableColumn id="9" xr3:uid="{3B1A8B4A-CD19-420A-8B55-D1E6E71036BF}" name="2016" dataDxfId="13"/>
+    <tableColumn id="10" xr3:uid="{8A13625C-A654-46AC-A558-DE0A972F322D}" name="2017" dataDxfId="12"/>
+    <tableColumn id="11" xr3:uid="{99E5B31D-42FA-47A4-B981-3A500BCD39D5}" name="2018" dataDxfId="11"/>
+    <tableColumn id="12" xr3:uid="{41FACBA7-3939-45A7-AB50-B7A958216469}" name="2019" dataDxfId="10"/>
+    <tableColumn id="13" xr3:uid="{1949E823-8768-46FD-8E24-872E7A0FC375}" name="2020" dataDxfId="9"/>
+    <tableColumn id="14" xr3:uid="{8E404941-341D-4DB3-A956-B66D4D2E8126}" name="2021" dataDxfId="8"/>
+    <tableColumn id="15" xr3:uid="{704B145E-914A-41F3-A348-5BCF98CDA78F}" name="2022" dataDxfId="7"/>
+    <tableColumn id="16" xr3:uid="{CFB54067-4688-4253-A746-1C1D1912493F}" name="2023" dataDxfId="6"/>
+    <tableColumn id="17" xr3:uid="{F286FA37-E091-4F76-9852-EC5DACED56CD}" name="2024" dataDxfId="5"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleLight1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -3037,12 +3021,12 @@
     <sortCondition ref="A1:A432"/>
   </sortState>
   <tableColumns count="8">
-    <tableColumn id="1" xr3:uid="{7B4D1A0E-D62F-437E-BB8E-B7F4E8C17935}" name="file_year" dataDxfId="5"/>
+    <tableColumn id="1" xr3:uid="{7B4D1A0E-D62F-437E-BB8E-B7F4E8C17935}" name="file_year" dataDxfId="4"/>
     <tableColumn id="2" xr3:uid="{9F291EAD-F124-4D48-8D78-B9F4726EF707}" name="variable"/>
-    <tableColumn id="3" xr3:uid="{748BF00D-E3D8-41D2-9E91-CC9252D1484B}" name="from_code" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{9383B21A-C12D-4E83-8D44-9DC1C9CD1EB0}" name="from_label" dataDxfId="3"/>
-    <tableColumn id="5" xr3:uid="{A1CCEB11-5D19-49DE-8619-3FEC9EE5883B}" name="to_code" dataDxfId="2"/>
-    <tableColumn id="6" xr3:uid="{2699A3D3-1402-4F0B-BBB9-FA37BEF08E86}" name="to_label" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{748BF00D-E3D8-41D2-9E91-CC9252D1484B}" name="from_code" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{9383B21A-C12D-4E83-8D44-9DC1C9CD1EB0}" name="from_label" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{A1CCEB11-5D19-49DE-8619-3FEC9EE5883B}" name="to_code" dataDxfId="1"/>
+    <tableColumn id="6" xr3:uid="{2699A3D3-1402-4F0B-BBB9-FA37BEF08E86}" name="to_label" dataDxfId="0"/>
     <tableColumn id="7" xr3:uid="{A806039F-1AC2-47A6-BDE5-CBEB771225F5}" name="review_flag"/>
     <tableColumn id="9" xr3:uid="{07280E7E-4939-49D5-ADA2-2FB50246FF53}" name="notes"/>
   </tableColumns>
@@ -3340,79 +3324,79 @@
   <dimension ref="A1:E4"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="27.85546875" style="34" customWidth="1"/>
-    <col min="2" max="2" width="31.7109375" style="34" customWidth="1"/>
-    <col min="3" max="3" width="78.42578125" style="35" customWidth="1"/>
-    <col min="4" max="4" width="79.85546875" style="34" customWidth="1"/>
-    <col min="5" max="5" width="53.5703125" style="35" customWidth="1"/>
+    <col min="1" max="1" width="27.85546875" style="28" customWidth="1"/>
+    <col min="2" max="2" width="31.7109375" style="28" customWidth="1"/>
+    <col min="3" max="3" width="78.42578125" style="29" customWidth="1"/>
+    <col min="4" max="4" width="79.85546875" style="28" customWidth="1"/>
+    <col min="5" max="5" width="53.5703125" style="29" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="33" t="s">
+      <c r="A1" s="27" t="s">
         <v>613</v>
       </c>
-      <c r="B1" s="33" t="s">
+      <c r="B1" s="27" t="s">
         <v>619</v>
       </c>
-      <c r="C1" s="38" t="s">
+      <c r="C1" s="32" t="s">
         <v>614</v>
       </c>
-      <c r="D1" s="37" t="s">
+      <c r="D1" s="31" t="s">
         <v>616</v>
       </c>
-      <c r="E1" s="39" t="s">
+      <c r="E1" s="33" t="s">
         <v>622</v>
       </c>
     </row>
     <row r="2" spans="1:5" ht="150" x14ac:dyDescent="0.25">
-      <c r="A2" s="40" t="s">
+      <c r="A2" s="34" t="s">
         <v>615</v>
       </c>
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="28" t="s">
         <v>618</v>
       </c>
-      <c r="C2" s="35" t="s">
+      <c r="C2" s="29" t="s">
         <v>625</v>
       </c>
-      <c r="D2" s="35" t="s">
+      <c r="D2" s="29" t="s">
         <v>623</v>
       </c>
-      <c r="E2" s="35" t="s">
+      <c r="E2" s="29" t="s">
         <v>624</v>
       </c>
     </row>
     <row r="3" spans="1:5" ht="270" x14ac:dyDescent="0.25">
-      <c r="A3" s="40" t="s">
+      <c r="A3" s="34" t="s">
         <v>617</v>
       </c>
-      <c r="B3" s="34" t="s">
+      <c r="B3" s="28" t="s">
         <v>618</v>
       </c>
-      <c r="C3" s="35" t="s">
+      <c r="C3" s="29" t="s">
         <v>626</v>
       </c>
-      <c r="D3" s="36" t="s">
+      <c r="D3" s="30" t="s">
+        <v>631</v>
+      </c>
+      <c r="E3" s="29" t="s">
         <v>628</v>
       </c>
-      <c r="E3" s="35" t="s">
+    </row>
+    <row r="4" spans="1:5" ht="165" x14ac:dyDescent="0.25">
+      <c r="A4" s="34" t="s">
+        <v>627</v>
+      </c>
+      <c r="B4" s="28" t="s">
+        <v>620</v>
+      </c>
+      <c r="C4" s="29" t="s">
         <v>629</v>
       </c>
-    </row>
-    <row r="4" spans="1:5" ht="165" x14ac:dyDescent="0.25">
-      <c r="A4" s="40" t="s">
-        <v>627</v>
-      </c>
-      <c r="B4" s="34" t="s">
-        <v>620</v>
-      </c>
-      <c r="C4" s="35" t="s">
+      <c r="D4" s="28" t="s">
+        <v>621</v>
+      </c>
+      <c r="E4" s="29" t="s">
         <v>630</v>
-      </c>
-      <c r="D4" s="34" t="s">
-        <v>621</v>
-      </c>
-      <c r="E4" s="35" t="s">
-        <v>631</v>
       </c>
     </row>
   </sheetData>
@@ -18830,14 +18814,14 @@
       <c r="F19" s="22"/>
       <c r="G19" s="20"/>
     </row>
-    <row r="20" spans="1:7" s="32" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="29" t="s">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A20" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B20" s="27" t="s">
+      <c r="B20" s="14" t="s">
         <v>522</v>
       </c>
-      <c r="C20" s="28" t="b">
+      <c r="C20" s="26" t="b">
         <v>0</v>
       </c>
       <c r="D20" s="6">
@@ -18846,27 +18830,23 @@
       <c r="E20" s="6" t="s">
         <v>420</v>
       </c>
-      <c r="F20" s="30"/>
-      <c r="G20" s="31"/>
-    </row>
-    <row r="21" spans="1:7" s="32" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="29" t="s">
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A21" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B21" s="27" t="s">
+      <c r="B21" s="14" t="s">
         <v>522</v>
       </c>
-      <c r="C21" s="28" t="b">
-        <v>0</v>
-      </c>
-      <c r="D21" s="29">
+      <c r="C21" s="26" t="b">
+        <v>0</v>
+      </c>
+      <c r="D21" s="6">
         <v>3</v>
       </c>
-      <c r="E21" s="27" t="s">
+      <c r="E21" s="14" t="s">
         <v>424</v>
       </c>
-      <c r="F21" s="30"/>
-      <c r="G21" s="31"/>
     </row>
     <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="6" t="s">
